--- a/Step2/Outputs/Low_comparison.xlsx
+++ b/Step2/Outputs/Low_comparison.xlsx
@@ -538,19 +538,19 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>667.1607858300158</v>
+        <v>667.1607831283582</v>
       </c>
       <c r="D4">
-        <v>462.969302350004</v>
+        <v>462.9693006077541</v>
       </c>
       <c r="E4">
-        <v>632.9636173099898</v>
+        <v>632.9636147711681</v>
       </c>
       <c r="F4">
-        <v>876.9489258799913</v>
+        <v>876.9489224470526</v>
       </c>
       <c r="G4">
-        <v>964.9349152000068</v>
+        <v>964.9349119139406</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -559,19 +559,19 @@
         <v>15</v>
       </c>
       <c r="L4">
-        <v>-104.3852381159668</v>
+        <v>-104.3852384992497</v>
       </c>
       <c r="M4">
-        <v>-325.9728451800256</v>
+        <v>-325.9728441568441</v>
       </c>
       <c r="N4">
-        <v>-717.9525004799725</v>
+        <v>-717.9524976223984</v>
       </c>
       <c r="O4">
-        <v>-1192.925094279999</v>
+        <v>-1192.925089150187</v>
       </c>
       <c r="P4">
-        <v>-2234.857762620006</v>
+        <v>-2234.857752817319</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -580,19 +580,19 @@
         <v>16</v>
       </c>
       <c r="U4">
-        <v>-415.7791193819794</v>
+        <v>-415.7791172772595</v>
       </c>
       <c r="V4">
-        <v>-561.97273365</v>
+        <v>-561.9727304953049</v>
       </c>
       <c r="W4">
-        <v>-1061.948965710013</v>
+        <v>-1061.948959573918</v>
       </c>
       <c r="X4">
-        <v>-1674.91962569001</v>
+        <v>-1674.919616008632</v>
       </c>
       <c r="Y4">
-        <v>-2980.855605689994</v>
+        <v>-2980.855588749564</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -601,19 +601,19 @@
         <v>17</v>
       </c>
       <c r="AD4">
-        <v>-203.3931667919996</v>
+        <v>-203.3931654923454</v>
       </c>
       <c r="AE4">
-        <v>-202.9925742700016</v>
+        <v>-202.9925729363958</v>
       </c>
       <c r="AF4">
-        <v>-351.9885142200019</v>
+        <v>-351.9885119272185</v>
       </c>
       <c r="AG4">
-        <v>-545.9811962899948</v>
+        <v>-545.9811927116134</v>
       </c>
       <c r="AH4">
-        <v>-1121.958597479998</v>
+        <v>-1121.958590168486</v>
       </c>
       <c r="AK4">
         <v>10</v>
@@ -622,19 +622,19 @@
         <v>11</v>
       </c>
       <c r="AM4">
-        <v>-2420.966291868099</v>
+        <v>-2420.966276832507</v>
       </c>
       <c r="AN4">
-        <v>-1312.981921000057</v>
+        <v>-1312.981912807474</v>
       </c>
       <c r="AO4">
-        <v>-1993.972017769934</v>
+        <v>-1993.972005367861</v>
       </c>
       <c r="AP4">
-        <v>-2856.96004248003</v>
+        <v>-2856.960024745291</v>
       </c>
       <c r="AQ4">
-        <v>-7045.902005829936</v>
+        <v>-7045.901962014556</v>
       </c>
       <c r="AT4">
         <v>10</v>
@@ -643,19 +643,19 @@
         <v>12</v>
       </c>
       <c r="AV4">
-        <v>-1904.31297530992</v>
+        <v>-1904.312965270947</v>
       </c>
       <c r="AW4">
-        <v>-1316.922360079814</v>
+        <v>-1316.922353865215</v>
       </c>
       <c r="AX4">
-        <v>-2045.909995989947</v>
+        <v>-2045.909985093021</v>
       </c>
       <c r="AY4">
-        <v>-2888.864757899966</v>
+        <v>-2888.864742808844</v>
       </c>
       <c r="AZ4">
-        <v>-6870.678412940048</v>
+        <v>-6870.678375435964</v>
       </c>
     </row>
     <row r="5" spans="1:52">
@@ -666,19 +666,19 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>149.481527777999</v>
+        <v>149.481526377328</v>
       </c>
       <c r="D5">
-        <v>75.44404494999981</v>
+        <v>75.44404425446646</v>
       </c>
       <c r="E5">
-        <v>75.84520913999404</v>
+        <v>75.84520859689746</v>
       </c>
       <c r="F5">
-        <v>90.84562834999542</v>
+        <v>90.8456278514459</v>
       </c>
       <c r="G5">
-        <v>65.4495912900029</v>
+        <v>65.44959120614567</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -687,19 +687,19 @@
         <v>15</v>
       </c>
       <c r="L5">
-        <v>101.5419609119926</v>
+        <v>101.5419595590974</v>
       </c>
       <c r="M5">
-        <v>-92.05868883998846</v>
+        <v>-92.05868794069464</v>
       </c>
       <c r="N5">
-        <v>-302.9466745099926</v>
+        <v>-302.9466712892463</v>
       </c>
       <c r="O5">
-        <v>-538.2221973700034</v>
+        <v>-538.2221917579591</v>
       </c>
       <c r="P5">
-        <v>-1095.476765420015</v>
+        <v>-1095.476753587627</v>
       </c>
       <c r="S5">
         <v>2</v>
@@ -708,19 +708,19 @@
         <v>16</v>
       </c>
       <c r="U5">
-        <v>-171.5404075260012</v>
+        <v>-171.5404057974774</v>
       </c>
       <c r="V5">
-        <v>-349.7107708099902</v>
+        <v>-349.7107668144999</v>
       </c>
       <c r="W5">
-        <v>-714.4507766900133</v>
+        <v>-714.4507684000746</v>
       </c>
       <c r="X5">
-        <v>-1142.406961490007</v>
+        <v>-1142.406948132524</v>
       </c>
       <c r="Y5">
-        <v>-2011.894555129998</v>
+        <v>-2011.894531583636</v>
       </c>
       <c r="AB5">
         <v>2</v>
@@ -729,19 +729,19 @@
         <v>17</v>
       </c>
       <c r="AD5">
-        <v>-129.0664922700034</v>
+        <v>-129.0664906463853</v>
       </c>
       <c r="AE5">
-        <v>-131.2737640300029</v>
+        <v>-131.2737622958039</v>
       </c>
       <c r="AF5">
-        <v>-221.7445290900005</v>
+        <v>-221.7445261607517</v>
       </c>
       <c r="AG5">
-        <v>-341.6516016499982</v>
+        <v>-341.6515969313923</v>
       </c>
       <c r="AH5">
-        <v>-763.9296411399991</v>
+        <v>-763.9296307959521</v>
       </c>
       <c r="AK5">
         <v>2</v>
@@ -750,19 +750,19 @@
         <v>11</v>
       </c>
       <c r="AM5">
-        <v>-1322.345293787992</v>
+        <v>-1322.345278313893</v>
       </c>
       <c r="AN5">
-        <v>-712.9012421700318</v>
+        <v>-712.9012337894383</v>
       </c>
       <c r="AO5">
-        <v>-1086.446436400001</v>
+        <v>-1086.446423664325</v>
       </c>
       <c r="AP5">
-        <v>-1551.057809069971</v>
+        <v>-1551.057790863371</v>
       </c>
       <c r="AQ5">
-        <v>-3825.993546829981</v>
+        <v>-3825.993501939389</v>
       </c>
       <c r="AT5">
         <v>2</v>
@@ -771,19 +771,19 @@
         <v>12</v>
       </c>
       <c r="AV5">
-        <v>-932.9868473160168</v>
+        <v>-932.9868358002786</v>
       </c>
       <c r="AW5">
-        <v>-827.3251220200327</v>
+        <v>-827.3251117495238</v>
       </c>
       <c r="AX5">
-        <v>-1271.327985299969</v>
+        <v>-1271.327969835096</v>
       </c>
       <c r="AY5">
-        <v>-1797.081979090042</v>
+        <v>-1797.081956232243</v>
       </c>
       <c r="AZ5">
-        <v>-4366.753062409989</v>
+        <v>-4366.753008565618</v>
       </c>
     </row>
     <row r="6" spans="1:52">
@@ -794,19 +794,19 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>616.6110249239937</v>
+        <v>616.61102113179</v>
       </c>
       <c r="D6">
-        <v>470.8690807800122</v>
+        <v>470.8690777787451</v>
       </c>
       <c r="E6">
-        <v>655.8030906900094</v>
+        <v>655.8030865474066</v>
       </c>
       <c r="F6">
-        <v>905.7153564299952</v>
+        <v>905.7153506319736</v>
       </c>
       <c r="G6">
-        <v>1005.616970890016</v>
+        <v>1005.616965296696</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -815,19 +815,19 @@
         <v>15</v>
       </c>
       <c r="L6">
-        <v>-139.8111178199979</v>
+        <v>-139.8111158790198</v>
       </c>
       <c r="M6">
-        <v>-255.9776511900054</v>
+        <v>-255.9776485980183</v>
       </c>
       <c r="N6">
-        <v>-555.9130494200072</v>
+        <v>-555.9130444176335</v>
       </c>
       <c r="O6">
-        <v>-932.8374943300004</v>
+        <v>-932.8374862739512</v>
       </c>
       <c r="P6">
-        <v>-1727.633178420001</v>
+        <v>-1727.633164906074</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -836,19 +836,19 @@
         <v>16</v>
       </c>
       <c r="U6">
-        <v>-348.4574658540023</v>
+        <v>-348.4574644116728</v>
       </c>
       <c r="V6">
-        <v>-443.839306439997</v>
+        <v>-443.8393046850979</v>
       </c>
       <c r="W6">
-        <v>-815.6786947300025</v>
+        <v>-815.6786915636112</v>
       </c>
       <c r="X6">
-        <v>-1293.507667420003</v>
+        <v>-1293.507662357373</v>
       </c>
       <c r="Y6">
-        <v>-2311.144169239997</v>
+        <v>-2311.144160059033</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -857,19 +857,19 @@
         <v>17</v>
       </c>
       <c r="AD6">
-        <v>-154.7297648580015</v>
+        <v>-154.729764275683</v>
       </c>
       <c r="AE6">
-        <v>-159.9359970200003</v>
+        <v>-159.9359964043615</v>
       </c>
       <c r="AF6">
-        <v>-258.8826363000016</v>
+        <v>-258.8826352010137</v>
       </c>
       <c r="AG6">
-        <v>-388.8295812999959</v>
+        <v>-388.8295796379261</v>
       </c>
       <c r="AH6">
-        <v>-798.6377187799999</v>
+        <v>-798.6377155491127</v>
       </c>
       <c r="AK6">
         <v>9</v>
@@ -878,19 +878,19 @@
         <v>11</v>
       </c>
       <c r="AM6">
-        <v>-2328.785198886006</v>
+        <v>-2328.785180617066</v>
       </c>
       <c r="AN6">
-        <v>-1259.454317350057</v>
+        <v>-1259.454307469307</v>
       </c>
       <c r="AO6">
-        <v>-1918.159847229836</v>
+        <v>-1918.159832157806</v>
       </c>
       <c r="AP6">
-        <v>-2744.799683579942</v>
+        <v>-2744.799662083999</v>
       </c>
       <c r="AQ6">
-        <v>-6762.054061939984</v>
+        <v>-6762.054008946638</v>
       </c>
       <c r="AT6">
         <v>9</v>
@@ -899,19 +899,19 @@
         <v>12</v>
       </c>
       <c r="AV6">
-        <v>-1541.497945332012</v>
+        <v>-1541.497937820299</v>
       </c>
       <c r="AW6">
-        <v>-915.6680140599492</v>
+        <v>-915.6680105710692</v>
       </c>
       <c r="AX6">
-        <v>-1245.551678350021</v>
+        <v>-1245.551673001814</v>
       </c>
       <c r="AY6">
-        <v>-1663.399509269962</v>
+        <v>-1663.399503446417</v>
       </c>
       <c r="AZ6">
-        <v>-4694.481944469953</v>
+        <v>-4694.48192209618</v>
       </c>
     </row>
     <row r="7" spans="1:52">
@@ -922,19 +922,19 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>38.87687398800017</v>
+        <v>38.87687330065501</v>
       </c>
       <c r="D7">
-        <v>20.00140138000006</v>
+        <v>20.00140092290258</v>
       </c>
       <c r="E7">
-        <v>17.55416392000006</v>
+        <v>17.5541633806024</v>
       </c>
       <c r="F7">
-        <v>17.10714889999963</v>
+        <v>17.10714821989632</v>
       </c>
       <c r="G7">
-        <v>3.316857339999842</v>
+        <v>3.316856606379588</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -943,19 +943,19 @@
         <v>15</v>
       </c>
       <c r="L7">
-        <v>36.67966045800222</v>
+        <v>36.67966031588549</v>
       </c>
       <c r="M7">
-        <v>-22.79225481999947</v>
+        <v>-22.79225445396969</v>
       </c>
       <c r="N7">
-        <v>-82.3753991500007</v>
+        <v>-82.37539823876523</v>
       </c>
       <c r="O7">
-        <v>-156.3017355000002</v>
+        <v>-156.3017339404214</v>
       </c>
       <c r="P7">
-        <v>-329.9457997800027</v>
+        <v>-329.9457965713009</v>
       </c>
       <c r="S7">
         <v>7</v>
@@ -964,19 +964,19 @@
         <v>16</v>
       </c>
       <c r="U7">
-        <v>-44.670374549999</v>
+        <v>-44.670373983231</v>
       </c>
       <c r="V7">
-        <v>-104.9263266799999</v>
+        <v>-104.9263257521952</v>
       </c>
       <c r="W7">
-        <v>-217.7479051700011</v>
+        <v>-217.7479033307682</v>
       </c>
       <c r="X7">
-        <v>-354.4649701199987</v>
+        <v>-354.464967202578</v>
       </c>
       <c r="Y7">
-        <v>-625.7949174599999</v>
+        <v>-625.7949123784711</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -985,19 +985,19 @@
         <v>17</v>
       </c>
       <c r="AD7">
-        <v>-48.16084264799883</v>
+        <v>-48.16084225229633</v>
       </c>
       <c r="AE7">
-        <v>-46.4770150900008</v>
+        <v>-46.47701471879964</v>
       </c>
       <c r="AF7">
-        <v>-81.50638780999998</v>
+        <v>-81.50638712921636</v>
       </c>
       <c r="AG7">
-        <v>-122.431347270001</v>
+        <v>-122.4313462166165</v>
       </c>
       <c r="AH7">
-        <v>-272.7577419400009</v>
+        <v>-272.7577397301211</v>
       </c>
       <c r="AK7">
         <v>7</v>
@@ -1006,19 +1006,19 @@
         <v>11</v>
       </c>
       <c r="AM7">
-        <v>-412.505269583995</v>
+        <v>-412.5052667082491</v>
       </c>
       <c r="AN7">
-        <v>-222.940721529998</v>
+        <v>-222.9407199908092</v>
       </c>
       <c r="AO7">
-        <v>-340.5826928700008</v>
+        <v>-340.582690508938</v>
       </c>
       <c r="AP7">
-        <v>-484.9116178599943</v>
+        <v>-484.9116144509681</v>
       </c>
       <c r="AQ7">
-        <v>-1196.211479660004</v>
+        <v>-1196.211471319151</v>
       </c>
       <c r="AT7">
         <v>7</v>
@@ -1027,19 +1027,19 @@
         <v>12</v>
       </c>
       <c r="AV7">
-        <v>-321.6359895419955</v>
+        <v>-321.6359868499858</v>
       </c>
       <c r="AW7">
-        <v>-245.7769855799961</v>
+        <v>-245.776983502441</v>
       </c>
       <c r="AX7">
-        <v>-370.2858090200025</v>
+        <v>-370.2858060181534</v>
       </c>
       <c r="AY7">
-        <v>-482.2146765000034</v>
+        <v>-482.2146721212521</v>
       </c>
       <c r="AZ7">
-        <v>-1280.290798990012</v>
+        <v>-1280.290788461152</v>
       </c>
     </row>
     <row r="8" spans="1:52">
@@ -1050,19 +1050,19 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>137.473422414002</v>
+        <v>137.473422736487</v>
       </c>
       <c r="D8">
-        <v>73.07814291000159</v>
+        <v>73.07814317034627</v>
       </c>
       <c r="E8">
-        <v>82.68545394000103</v>
+        <v>82.68545429883852</v>
       </c>
       <c r="F8">
-        <v>102.5012904800005</v>
+        <v>102.5012909173502</v>
       </c>
       <c r="G8">
-        <v>68.07768005000071</v>
+        <v>68.07768065011442</v>
       </c>
       <c r="J8">
         <v>8</v>
@@ -1071,19 +1071,19 @@
         <v>15</v>
       </c>
       <c r="L8">
-        <v>66.99849418199665</v>
+        <v>66.99849403334883</v>
       </c>
       <c r="M8">
-        <v>-89.26777753000715</v>
+        <v>-89.2677778134057</v>
       </c>
       <c r="N8">
-        <v>-273.1211996799939</v>
+        <v>-273.1212002003122</v>
       </c>
       <c r="O8">
-        <v>-469.0197189000101</v>
+        <v>-469.0197195291621</v>
       </c>
       <c r="P8">
-        <v>-934.2910867899992</v>
+        <v>-934.2910878556432</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1092,19 +1092,19 @@
         <v>16</v>
       </c>
       <c r="U8">
-        <v>-124.3585278359969</v>
+        <v>-124.3585280118405</v>
       </c>
       <c r="V8">
-        <v>-252.0181394800038</v>
+        <v>-252.0181396226562</v>
       </c>
       <c r="W8">
-        <v>-519.2936285999986</v>
+        <v>-519.293628878735</v>
       </c>
       <c r="X8">
-        <v>-821.8367835500067</v>
+        <v>-821.8367840016763</v>
       </c>
       <c r="Y8">
-        <v>-1440.16685189999</v>
+        <v>-1440.166852657494</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1113,19 +1113,19 @@
         <v>17</v>
       </c>
       <c r="AD8">
-        <v>-113.3095535639977</v>
+        <v>-113.3095535922994</v>
       </c>
       <c r="AE8">
-        <v>-134.25192066</v>
+        <v>-134.2519205557974</v>
       </c>
       <c r="AF8">
-        <v>-234.6719803700034</v>
+        <v>-234.6719801886802</v>
       </c>
       <c r="AG8">
-        <v>-356.1128807700043</v>
+        <v>-356.1128805728786</v>
       </c>
       <c r="AH8">
-        <v>-753.2158544400063</v>
+        <v>-753.2158540797582</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -1134,19 +1134,19 @@
         <v>11</v>
       </c>
       <c r="AM8">
-        <v>-1454.015676798052</v>
+        <v>-1454.015673891307</v>
       </c>
       <c r="AN8">
-        <v>-789.7100445199176</v>
+        <v>-789.7100430182763</v>
       </c>
       <c r="AO8">
-        <v>-1199.598401750001</v>
+        <v>-1199.598399477531</v>
       </c>
       <c r="AP8">
-        <v>-1717.736639749957</v>
+        <v>-1717.73663650747</v>
       </c>
       <c r="AQ8">
-        <v>-4227.952340499993</v>
+        <v>-4227.952332468994</v>
       </c>
       <c r="AT8">
         <v>8</v>
@@ -1155,19 +1155,19 @@
         <v>12</v>
       </c>
       <c r="AV8">
-        <v>-799.057089869988</v>
+        <v>-799.0570902946783</v>
       </c>
       <c r="AW8">
-        <v>-676.6469473500256</v>
+        <v>-676.6469473998804</v>
       </c>
       <c r="AX8">
-        <v>-1065.060268459987</v>
+        <v>-1065.060267999499</v>
       </c>
       <c r="AY8">
-        <v>-1469.881443629994</v>
+        <v>-1469.881443934006</v>
       </c>
       <c r="AZ8">
-        <v>-3317.481241760026</v>
+        <v>-3317.481242669768</v>
       </c>
     </row>
     <row r="9" spans="1:52">
@@ -1178,19 +1178,19 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>253.1718001260051</v>
+        <v>253.171800389493</v>
       </c>
       <c r="D9">
-        <v>173.9812578899928</v>
+        <v>173.9812580808793</v>
       </c>
       <c r="E9">
-        <v>200.978305040002</v>
+        <v>200.9783053389311</v>
       </c>
       <c r="F9">
-        <v>262.9700928999973</v>
+        <v>262.9700932352916</v>
       </c>
       <c r="G9">
-        <v>303.9668723600007</v>
+        <v>303.9668727992812</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1199,19 +1199,19 @@
         <v>15</v>
       </c>
       <c r="L9">
-        <v>29.39670911999201</v>
+        <v>29.39670921653305</v>
       </c>
       <c r="M9">
-        <v>-116.989793960005</v>
+        <v>-116.9897940292321</v>
       </c>
       <c r="N9">
-        <v>-307.9705703100153</v>
+        <v>-307.9705705835149</v>
       </c>
       <c r="O9">
-        <v>-536.9466098599987</v>
+        <v>-536.9466103192135</v>
       </c>
       <c r="P9">
-        <v>-1089.891306779995</v>
+        <v>-1089.891307740774</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1220,19 +1220,19 @@
         <v>16</v>
       </c>
       <c r="U9">
-        <v>-186.5792687279918</v>
+        <v>-186.5792689631435</v>
       </c>
       <c r="V9">
-        <v>-302.9687359200016</v>
+        <v>-302.9687362783334</v>
       </c>
       <c r="W9">
-        <v>-584.9398636199967</v>
+        <v>-584.9398643086934</v>
       </c>
       <c r="X9">
-        <v>-940.9038024699984</v>
+        <v>-940.9038035754402</v>
       </c>
       <c r="Y9">
-        <v>-1698.824756520004</v>
+        <v>-1698.824758472882</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1241,19 +1241,19 @@
         <v>17</v>
       </c>
       <c r="AD9">
-        <v>-126.5862772739993</v>
+        <v>-126.5862774430698</v>
       </c>
       <c r="AE9">
-        <v>-120.9876896200003</v>
+        <v>-120.9876898038556</v>
       </c>
       <c r="AF9">
-        <v>-205.9807922300006</v>
+        <v>-205.9807925289388</v>
       </c>
       <c r="AG9">
-        <v>-311.9716371799987</v>
+        <v>-311.9716375917415</v>
       </c>
       <c r="AH9">
-        <v>-649.9418614700026</v>
+        <v>-649.9418622547091</v>
       </c>
       <c r="AK9">
         <v>5</v>
@@ -1262,19 +1262,19 @@
         <v>11</v>
       </c>
       <c r="AM9">
-        <v>-993.5004221099808</v>
+        <v>-993.5004251534629</v>
       </c>
       <c r="AN9">
-        <v>-535.945519550005</v>
+        <v>-535.9455211860623</v>
       </c>
       <c r="AO9">
-        <v>-820.9175207999942</v>
+        <v>-820.9175233319402</v>
       </c>
       <c r="AP9">
-        <v>-1170.883220629999</v>
+        <v>-1170.883224199315</v>
       </c>
       <c r="AQ9">
-        <v>-2883.710695469977</v>
+        <v>-2883.71070427882</v>
       </c>
       <c r="AT9">
         <v>5</v>
@@ -1283,19 +1283,19 @@
         <v>12</v>
       </c>
       <c r="AV9">
-        <v>-868.1122161840103</v>
+        <v>-868.1122171682728</v>
       </c>
       <c r="AW9">
-        <v>-628.9420222699991</v>
+        <v>-628.9420229234602</v>
       </c>
       <c r="AX9">
-        <v>-896.9190402700115</v>
+        <v>-896.9190414181867</v>
       </c>
       <c r="AY9">
-        <v>-1162.901431019971</v>
+        <v>-1162.90143202091</v>
       </c>
       <c r="AZ9">
-        <v>-3185.69633157998</v>
+        <v>-3185.69633490171</v>
       </c>
     </row>
     <row r="10" spans="1:52">
@@ -1306,19 +1306,19 @@
         <v>14</v>
       </c>
       <c r="C10">
-        <v>138.7923016560016</v>
+        <v>138.7923010938675</v>
       </c>
       <c r="D10">
-        <v>76.13262220999604</v>
+        <v>76.13262189257512</v>
       </c>
       <c r="E10">
-        <v>89.19773237999834</v>
+        <v>89.19773199745759</v>
       </c>
       <c r="F10">
-        <v>108.2853118799967</v>
+        <v>108.2853113886294</v>
       </c>
       <c r="G10">
-        <v>80.38454795000052</v>
+        <v>80.38454754596296</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -1327,19 +1327,19 @@
         <v>15</v>
       </c>
       <c r="L10">
-        <v>99.01172938200398</v>
+        <v>99.01172880697776</v>
       </c>
       <c r="M10">
-        <v>-45.02477631000511</v>
+        <v>-45.02477619187994</v>
       </c>
       <c r="N10">
-        <v>-198.0921555500026</v>
+        <v>-198.0921547768958</v>
       </c>
       <c r="O10">
-        <v>-370.1733692199887</v>
+        <v>-370.1733677687007</v>
       </c>
       <c r="P10">
-        <v>-803.3861627299993</v>
+        <v>-803.3861595209783</v>
       </c>
       <c r="S10">
         <v>3</v>
@@ -1348,19 +1348,19 @@
         <v>16</v>
       </c>
       <c r="U10">
-        <v>-143.5470199560041</v>
+        <v>-143.5470193039182</v>
       </c>
       <c r="V10">
-        <v>-277.1659578399958</v>
+        <v>-277.1659565546033</v>
       </c>
       <c r="W10">
-        <v>-560.330459089997</v>
+        <v>-560.330456448879</v>
       </c>
       <c r="X10">
-        <v>-904.5056101100164</v>
+        <v>-904.505605854054</v>
       </c>
       <c r="Y10">
-        <v>-1587.87968523</v>
+        <v>-1587.879677785182</v>
       </c>
       <c r="AB10">
         <v>3</v>
@@ -1369,19 +1369,19 @@
         <v>17</v>
       </c>
       <c r="AD10">
-        <v>-121.2709614300011</v>
+        <v>-121.2709608154983</v>
       </c>
       <c r="AE10">
-        <v>-115.0643255999994</v>
+        <v>-115.0643250408302</v>
       </c>
       <c r="AF10">
-        <v>-195.1188065900042</v>
+        <v>-195.1188056192868</v>
       </c>
       <c r="AG10">
-        <v>-298.1709862500029</v>
+        <v>-298.1709847373231</v>
       </c>
       <c r="AH10">
-        <v>-627.36707243</v>
+        <v>-627.3670692746118</v>
       </c>
       <c r="AK10">
         <v>3</v>
@@ -1390,19 +1390,19 @@
         <v>11</v>
       </c>
       <c r="AM10">
-        <v>-1090.021959618003</v>
+        <v>-1090.02195439249</v>
       </c>
       <c r="AN10">
-        <v>-587.5496215299863</v>
+        <v>-587.549618689045</v>
       </c>
       <c r="AO10">
-        <v>-894.8462210400612</v>
+        <v>-894.8462167233811</v>
       </c>
       <c r="AP10">
-        <v>-1279.209846919992</v>
+        <v>-1279.209840799245</v>
       </c>
       <c r="AQ10">
-        <v>-3152.968537279972</v>
+        <v>-3152.968522124538</v>
       </c>
       <c r="AT10">
         <v>3</v>
@@ -1411,19 +1411,19 @@
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>-767.9127144840095</v>
+        <v>-767.9127109806577</v>
       </c>
       <c r="AW10">
-        <v>-552.3460867600006</v>
+        <v>-552.3460844817964</v>
       </c>
       <c r="AX10">
-        <v>-895.473763329981</v>
+        <v>-895.4737594552716</v>
       </c>
       <c r="AY10">
-        <v>-1202.626782450032</v>
+        <v>-1202.626777386198</v>
       </c>
       <c r="AZ10">
-        <v>-3080.573792560004</v>
+        <v>-3080.573778674268</v>
       </c>
     </row>
     <row r="11" spans="1:52">
@@ -1434,19 +1434,19 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>86.74420997399966</v>
+        <v>86.74420999150061</v>
       </c>
       <c r="D11">
-        <v>52.9999766499991</v>
+        <v>52.9999766275364</v>
       </c>
       <c r="E11">
-        <v>66.99997212000017</v>
+        <v>66.99997214228461</v>
       </c>
       <c r="F11">
-        <v>84.71308593000094</v>
+        <v>84.71308596337849</v>
       </c>
       <c r="G11">
-        <v>74.56559242000003</v>
+        <v>74.56559238728914</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1455,19 +1455,19 @@
         <v>15</v>
       </c>
       <c r="L11">
-        <v>66.77695816800042</v>
+        <v>66.77695806946213</v>
       </c>
       <c r="M11">
-        <v>-1.1950001862715E-05</v>
+        <v>-1.20099193736678E-05</v>
       </c>
       <c r="N11">
-        <v>-70.14748184999553</v>
+        <v>-70.14748196851906</v>
       </c>
       <c r="O11">
-        <v>-146.0080712600047</v>
+        <v>-146.0080714876513</v>
       </c>
       <c r="P11">
-        <v>-360.8848580099966</v>
+        <v>-360.8848583319541</v>
       </c>
       <c r="S11">
         <v>6</v>
@@ -1476,19 +1476,19 @@
         <v>16</v>
       </c>
       <c r="U11">
-        <v>-90.94419992999974</v>
+        <v>-90.94419988001393</v>
       </c>
       <c r="V11">
-        <v>-155.0080451999966</v>
+        <v>-155.0080450846508</v>
       </c>
       <c r="W11">
-        <v>-306.8767188699985</v>
+        <v>-306.8767187455014</v>
       </c>
       <c r="X11">
-        <v>-494.0322505000022</v>
+        <v>-494.0322502890085</v>
       </c>
       <c r="Y11">
-        <v>-883.6301773999985</v>
+        <v>-883.6301769786514</v>
       </c>
       <c r="AB11">
         <v>6</v>
@@ -1497,19 +1497,19 @@
         <v>17</v>
       </c>
       <c r="AD11">
-        <v>-74.74908826199999</v>
+        <v>-74.74908824867089</v>
       </c>
       <c r="AE11">
-        <v>-68.72122005000165</v>
+        <v>-68.72122003230652</v>
       </c>
       <c r="AF11">
-        <v>-113.4424530200004</v>
+        <v>-113.4424530036313</v>
       </c>
       <c r="AG11">
-        <v>-167.4505604699989</v>
+        <v>-167.4505603967782</v>
       </c>
       <c r="AH11">
-        <v>-360.9011021999986</v>
+        <v>-360.9011019645595</v>
       </c>
       <c r="AK11">
         <v>6</v>
@@ -1518,19 +1518,19 @@
         <v>11</v>
       </c>
       <c r="AM11">
-        <v>-599.831763197988</v>
+        <v>-599.8317646408796</v>
       </c>
       <c r="AN11">
-        <v>-321.0486250499962</v>
+        <v>-321.0486258157034</v>
       </c>
       <c r="AO11">
-        <v>-492.3598091899912</v>
+        <v>-492.3598103798795</v>
       </c>
       <c r="AP11">
-        <v>-704.1053498900001</v>
+        <v>-704.1053515794702</v>
       </c>
       <c r="AQ11">
-        <v>-1734.259323120001</v>
+        <v>-1734.259327328487</v>
       </c>
       <c r="AT11">
         <v>6</v>
@@ -1539,19 +1539,19 @@
         <v>12</v>
       </c>
       <c r="AV11">
-        <v>-479.1830153159899</v>
+        <v>-479.1830151756367</v>
       </c>
       <c r="AW11">
-        <v>-253.0161353899966</v>
+        <v>-253.0161351147762</v>
       </c>
       <c r="AX11">
-        <v>-380.4585905400018</v>
+        <v>-380.4585904444321</v>
       </c>
       <c r="AY11">
-        <v>-505.1879146400024</v>
+        <v>-505.1879141893878</v>
       </c>
       <c r="AZ11">
-        <v>-1379.408152010008</v>
+        <v>-1379.408151352982</v>
       </c>
     </row>
     <row r="12" spans="1:52">
@@ -1562,19 +1562,19 @@
         <v>14</v>
       </c>
       <c r="C12">
-        <v>197.4020965080026</v>
+        <v>197.402096905781</v>
       </c>
       <c r="D12">
-        <v>143.0016528200003</v>
+        <v>143.001653100333</v>
       </c>
       <c r="E12">
-        <v>185.0025665899993</v>
+        <v>185.0025669203624</v>
       </c>
       <c r="F12">
-        <v>245.0040345700008</v>
+        <v>245.0040350328682</v>
       </c>
       <c r="G12">
-        <v>288.0039935199984</v>
+        <v>288.0039941710911</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -1583,19 +1583,19 @@
         <v>15</v>
       </c>
       <c r="L12">
-        <v>9.599302493992582</v>
+        <v>9.599302322731091</v>
       </c>
       <c r="M12">
-        <v>-49.00239261000024</v>
+        <v>-49.00239274411069</v>
       </c>
       <c r="N12">
-        <v>-145.0051937400094</v>
+        <v>-145.0051939905716</v>
       </c>
       <c r="O12">
-        <v>-266.0079675999987</v>
+        <v>-266.0079679793162</v>
       </c>
       <c r="P12">
-        <v>-560.0141549999935</v>
+        <v>-560.014155687044</v>
       </c>
       <c r="S12">
         <v>4</v>
@@ -1604,19 +1604,19 @@
         <v>16</v>
       </c>
       <c r="U12">
-        <v>-146.4006767280007</v>
+        <v>-146.40067692907</v>
       </c>
       <c r="V12">
-        <v>-196.002061980007</v>
+        <v>-196.0020621899239</v>
       </c>
       <c r="W12">
-        <v>-361.0039367700029</v>
+        <v>-361.003937099882</v>
       </c>
       <c r="X12">
-        <v>-569.0062697900012</v>
+        <v>-569.0062703275416</v>
       </c>
       <c r="Y12">
-        <v>-1000.011379149999</v>
+        <v>-1000.011380082802</v>
       </c>
       <c r="AB12">
         <v>4</v>
@@ -1625,19 +1625,19 @@
         <v>17</v>
       </c>
       <c r="AD12">
-        <v>-75.00099804000001</v>
+        <v>-75.00099806425351</v>
       </c>
       <c r="AE12">
-        <v>-71.00146449000113</v>
+        <v>-71.00146453026628</v>
       </c>
       <c r="AF12">
-        <v>-109.0029712400005</v>
+        <v>-109.0029712377786</v>
       </c>
       <c r="AG12">
-        <v>-160.0047706399992</v>
+        <v>-160.0047706586051</v>
       </c>
       <c r="AH12">
-        <v>-319.0090176899998</v>
+        <v>-319.009017763216</v>
       </c>
       <c r="AK12">
         <v>4</v>
@@ -1646,19 +1646,19 @@
         <v>11</v>
       </c>
       <c r="AM12">
-        <v>-567.0310835460041</v>
+        <v>-567.0310830335002</v>
       </c>
       <c r="AN12">
-        <v>-307.0169217199946</v>
+        <v>-307.0169214254129</v>
       </c>
       <c r="AO12">
-        <v>-466.0258028600074</v>
+        <v>-466.0258024633477</v>
       </c>
       <c r="AP12">
-        <v>-668.0365463399939</v>
+        <v>-668.0365457487751</v>
       </c>
       <c r="AQ12">
-        <v>-1644.090119519984</v>
+        <v>-1644.090118029417</v>
       </c>
       <c r="AT12">
         <v>4</v>
@@ -1667,19 +1667,19 @@
         <v>12</v>
       </c>
       <c r="AV12">
-        <v>-604.804234908006</v>
+        <v>-604.8042356263177</v>
       </c>
       <c r="AW12">
-        <v>-370.0024817100129</v>
+        <v>-370.0024824270368</v>
       </c>
       <c r="AX12">
-        <v>-412.0067825899896</v>
+        <v>-412.0067832106725</v>
       </c>
       <c r="AY12">
-        <v>-540.0120203299666</v>
+        <v>-540.0120213850678</v>
       </c>
       <c r="AZ12">
-        <v>-1638.027227499995</v>
+        <v>-1638.027229528452</v>
       </c>
     </row>
     <row r="13" spans="1:52">
@@ -1690,19 +1690,19 @@
         <v>14</v>
       </c>
       <c r="C13">
-        <v>11.82019946399998</v>
+        <v>11.82019936812674</v>
       </c>
       <c r="D13">
-        <v>3.935785529999862</v>
+        <v>3.935785488613419</v>
       </c>
       <c r="E13">
-        <v>1.936104179999916</v>
+        <v>1.936104130451781</v>
       </c>
       <c r="F13">
-        <v>-0.0622209900002417</v>
+        <v>-0.0622210035943453</v>
       </c>
       <c r="G13">
-        <v>-8.025672549999854</v>
+        <v>-8.025672497974369</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1711,19 +1711,19 @@
         <v>15</v>
       </c>
       <c r="L13">
-        <v>20.81298979199937</v>
+        <v>20.81298956313549</v>
       </c>
       <c r="M13">
-        <v>-4.93339252999931</v>
+        <v>-4.933392535190251</v>
       </c>
       <c r="N13">
-        <v>-26.66078008000022</v>
+        <v>-26.66077992481541</v>
       </c>
       <c r="O13">
-        <v>-48.35424359000081</v>
+        <v>-48.35424330920296</v>
       </c>
       <c r="P13">
-        <v>-119.6398726100001</v>
+        <v>-119.6398717717866</v>
       </c>
       <c r="S13">
         <v>1</v>
@@ -1732,19 +1732,19 @@
         <v>16</v>
       </c>
       <c r="U13">
-        <v>-15.43930329600016</v>
+        <v>-15.43930312270368</v>
       </c>
       <c r="V13">
-        <v>-42.55706432000079</v>
+        <v>-42.55706390852765</v>
       </c>
       <c r="W13">
-        <v>-92.04334551000012</v>
+        <v>-92.04334465792316</v>
       </c>
       <c r="X13">
-        <v>-149.4629103100001</v>
+        <v>-149.4629089471218</v>
       </c>
       <c r="Y13">
-        <v>-265.2687251500015</v>
+        <v>-265.2687227639863</v>
       </c>
       <c r="AB13">
         <v>1</v>
@@ -1753,19 +1753,19 @@
         <v>17</v>
       </c>
       <c r="AD13">
-        <v>-24.91125233400044</v>
+        <v>-24.91125211316603</v>
       </c>
       <c r="AE13">
-        <v>-26.72497249000003</v>
+        <v>-26.724972259796</v>
       </c>
       <c r="AF13">
-        <v>-48.48273367000002</v>
+        <v>-48.48273323843932</v>
       </c>
       <c r="AG13">
-        <v>-75.20612738000023</v>
+        <v>-75.2061267324425</v>
       </c>
       <c r="AH13">
-        <v>-156.2044580200001</v>
+        <v>-156.2044567059208</v>
       </c>
       <c r="AK13">
         <v>1</v>
@@ -1774,19 +1774,19 @@
         <v>11</v>
       </c>
       <c r="AM13">
-        <v>-114.063083322003</v>
+        <v>-114.0630823124047</v>
       </c>
       <c r="AN13">
-        <v>-61.37975476000065</v>
+        <v>-61.3797542133243</v>
       </c>
       <c r="AO13">
-        <v>-94.03492116999951</v>
+        <v>-94.03492033440124</v>
       </c>
       <c r="AP13">
-        <v>-134.6211796200005</v>
+        <v>-134.6211784248808</v>
       </c>
       <c r="AQ13">
-        <v>-330.6570935399986</v>
+        <v>-330.6570905937097</v>
       </c>
       <c r="AT13">
         <v>1</v>
@@ -1795,19 +1795,19 @@
         <v>12</v>
       </c>
       <c r="AV13">
-        <v>-155.4289843619972</v>
+        <v>-155.4289830696289</v>
       </c>
       <c r="AW13">
-        <v>-103.8377092599949</v>
+        <v>-103.8377084456442</v>
       </c>
       <c r="AX13">
-        <v>-166.1453354799978</v>
+        <v>-166.1453339267718</v>
       </c>
       <c r="AY13">
-        <v>-237.5563785600007</v>
+        <v>-237.5563763977498</v>
       </c>
       <c r="AZ13">
-        <v>-574.8927245999985</v>
+        <v>-574.8927196194109</v>
       </c>
     </row>
     <row r="14" spans="1:52">
@@ -1818,19 +1818,19 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>315.0000019559957</v>
+        <v>315.0000000520577</v>
       </c>
       <c r="D14">
-        <v>211.000001340004</v>
+        <v>211.0000000328218</v>
       </c>
       <c r="E14">
-        <v>280.0000017000093</v>
+        <v>280.0000000429063</v>
       </c>
       <c r="F14">
-        <v>387.0000024200053</v>
+        <v>387.0000000602377</v>
       </c>
       <c r="G14">
-        <v>468.0000029699986</v>
+        <v>468.0000000760629</v>
       </c>
       <c r="J14">
         <v>17</v>
@@ -1839,19 +1839,19 @@
         <v>15</v>
       </c>
       <c r="L14">
-        <v>16.7999996940016</v>
+        <v>16.79999997716732</v>
       </c>
       <c r="M14">
-        <v>-142.0000009800169</v>
+        <v>-142.0000000375439</v>
       </c>
       <c r="N14">
-        <v>-345.0000022500026</v>
+        <v>-345.0000000779946</v>
       </c>
       <c r="O14">
-        <v>-590.0000037700156</v>
+        <v>-590.0000001289336</v>
       </c>
       <c r="P14">
-        <v>-1211.000007370014</v>
+        <v>-1211.000000245196</v>
       </c>
       <c r="S14">
         <v>17</v>
@@ -1860,19 +1860,19 @@
         <v>16</v>
       </c>
       <c r="U14">
-        <v>-218.4000011700045</v>
+        <v>-218.4000000253909</v>
       </c>
       <c r="V14">
-        <v>-308.0000015600017</v>
+        <v>-308.0000000318505</v>
       </c>
       <c r="W14">
-        <v>-596.0000029600033</v>
+        <v>-596.0000000584496</v>
       </c>
       <c r="X14">
-        <v>-945.000004710004</v>
+        <v>-945.0000000944856</v>
       </c>
       <c r="Y14">
-        <v>-1691.000008499997</v>
+        <v>-1691.000000171733</v>
       </c>
       <c r="AB14">
         <v>17</v>
@@ -1881,19 +1881,19 @@
         <v>17</v>
       </c>
       <c r="AD14">
-        <v>-143.4000006420001</v>
+        <v>-143.4000000081496</v>
       </c>
       <c r="AE14">
-        <v>-136.0000006199998</v>
+        <v>-136.0000000056434</v>
       </c>
       <c r="AF14">
-        <v>-252.0000011000002</v>
+        <v>-252.0000000096925</v>
       </c>
       <c r="AG14">
-        <v>-399.0000016499998</v>
+        <v>-399.000000012933</v>
       </c>
       <c r="AH14">
-        <v>-794.0000032600019</v>
+        <v>-794.0000000282671</v>
       </c>
       <c r="AK14">
         <v>17</v>
@@ -1902,19 +1902,19 @@
         <v>11</v>
       </c>
       <c r="AM14">
-        <v>-1209.000007212031</v>
+        <v>-1209.0000001851</v>
       </c>
       <c r="AN14">
-        <v>-658.0000039099687</v>
+        <v>-658.0000001011649</v>
       </c>
       <c r="AO14">
-        <v>-997.0000059599552</v>
+        <v>-997.000000152664</v>
       </c>
       <c r="AP14">
-        <v>-1424.000008509989</v>
+        <v>-1424.000000218395</v>
       </c>
       <c r="AQ14">
-        <v>-3525.000021029948</v>
+        <v>-3525.000000537606</v>
       </c>
       <c r="AT14">
         <v>17</v>
@@ -1923,19 +1923,19 @@
         <v>12</v>
       </c>
       <c r="AV14">
-        <v>-907.2000048900372</v>
+        <v>-907.2000000968692</v>
       </c>
       <c r="AW14">
-        <v>-361.0000025300615</v>
+        <v>-361.0000000297587</v>
       </c>
       <c r="AX14">
-        <v>-628.0000037999635</v>
+        <v>-628.0000000717409</v>
       </c>
       <c r="AY14">
-        <v>-928.0000054200063</v>
+        <v>-928.0000001036024</v>
       </c>
       <c r="AZ14">
-        <v>-2726.000014699981</v>
+        <v>-2726.000000290158</v>
       </c>
     </row>
     <row r="15" spans="1:52">
@@ -1946,19 +1946,19 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>165.1678811640004</v>
+        <v>165.1678810518079</v>
       </c>
       <c r="D15">
-        <v>85.42660362000061</v>
+        <v>85.42660354783402</v>
       </c>
       <c r="E15">
-        <v>94.42660608999904</v>
+        <v>94.426606007788</v>
       </c>
       <c r="F15">
-        <v>125.139904749999</v>
+        <v>125.1399046503539</v>
       </c>
       <c r="G15">
-        <v>106.4266221500002</v>
+        <v>106.4266220241516</v>
       </c>
       <c r="J15">
         <v>15</v>
@@ -1967,19 +1967,19 @@
         <v>15</v>
       </c>
       <c r="L15">
-        <v>37.36783496999851</v>
+        <v>37.36783504777122</v>
       </c>
       <c r="M15">
-        <v>-113.4266059699985</v>
+        <v>-113.4266058767753</v>
       </c>
       <c r="N15">
-        <v>-304.9930870200042</v>
+        <v>-304.9930868663177</v>
       </c>
       <c r="O15">
-        <v>-506.5595703399995</v>
+        <v>-506.5595701166167</v>
       </c>
       <c r="P15">
-        <v>-964.1191282899964</v>
+        <v>-964.1191278673324</v>
       </c>
       <c r="S15">
         <v>15</v>
@@ -1988,19 +1988,19 @@
         <v>16</v>
       </c>
       <c r="U15">
-        <v>-133.5818499600027</v>
+        <v>-133.5818499401885</v>
       </c>
       <c r="V15">
-        <v>-225.3496996000013</v>
+        <v>-225.3496995814185</v>
       </c>
       <c r="W15">
-        <v>-447.0560421200025</v>
+        <v>-447.0560420856109</v>
       </c>
       <c r="X15">
-        <v>-718.1190324300005</v>
+        <v>-718.1190323858427</v>
       </c>
       <c r="Y15">
-        <v>-1316.028245409998</v>
+        <v>-1316.028245339854</v>
       </c>
       <c r="AB15">
         <v>15</v>
@@ -2009,19 +2009,19 @@
         <v>17</v>
       </c>
       <c r="AD15">
-        <v>-91.5818429760002</v>
+        <v>-91.581842963471</v>
       </c>
       <c r="AE15">
-        <v>-88.85317037999903</v>
+        <v>-88.8531703740764</v>
       </c>
       <c r="AF15">
-        <v>-160.7063421100002</v>
+        <v>-160.7063420859722</v>
       </c>
       <c r="AG15">
-        <v>-252.916155150001</v>
+        <v>-252.9161551112757</v>
       </c>
       <c r="AH15">
-        <v>-519.1889553500005</v>
+        <v>-519.1889552928487</v>
       </c>
       <c r="AK15">
         <v>15</v>
@@ -2030,19 +2030,19 @@
         <v>11</v>
       </c>
       <c r="AM15">
-        <v>-583.3429580700031</v>
+        <v>-583.3429575766095</v>
       </c>
       <c r="AN15">
-        <v>-316.412753060009</v>
+        <v>-316.4127527925884</v>
       </c>
       <c r="AO15">
-        <v>-480.1191311800067</v>
+        <v>-480.1191307742483</v>
       </c>
       <c r="AP15">
-        <v>-687.2521023999943</v>
+        <v>-687.2521018255575</v>
       </c>
       <c r="AQ15">
-        <v>-1695.916957470003</v>
+        <v>-1695.916956051802</v>
       </c>
       <c r="AT15">
         <v>15</v>
@@ -2051,19 +2051,19 @@
         <v>12</v>
       </c>
       <c r="AV15">
-        <v>-707.8491349080068</v>
+        <v>-707.8491346780793</v>
       </c>
       <c r="AW15">
-        <v>-416.4896049099989</v>
+        <v>-416.4896048036098</v>
       </c>
       <c r="AX15">
-        <v>-703.0491202400008</v>
+        <v>-703.049120130032</v>
       </c>
       <c r="AY15">
-        <v>-1024.32190314</v>
+        <v>-1024.321903092299</v>
       </c>
       <c r="AZ15">
-        <v>-2364.846678449998</v>
+        <v>-2364.846678296672</v>
       </c>
     </row>
     <row r="16" spans="1:52">
@@ -2074,19 +2074,19 @@
         <v>14</v>
       </c>
       <c r="C16">
-        <v>161.0655607559993</v>
+        <v>161.0655601307444</v>
       </c>
       <c r="D16">
-        <v>97.92844689000049</v>
+        <v>97.92844647140282</v>
       </c>
       <c r="E16">
-        <v>118.1356062599998</v>
+        <v>118.1356057487001</v>
       </c>
       <c r="F16">
-        <v>162.5141410700007</v>
+        <v>162.5141403440311</v>
       </c>
       <c r="G16">
-        <v>150.3069754199987</v>
+        <v>150.306974628641</v>
       </c>
       <c r="J16">
         <v>16</v>
@@ -2095,19 +2095,19 @@
         <v>15</v>
       </c>
       <c r="L16">
-        <v>45.10284816600324</v>
+        <v>45.10284813426188</v>
       </c>
       <c r="M16">
-        <v>-95.92845343000226</v>
+        <v>-95.92845307350215</v>
       </c>
       <c r="N16">
-        <v>-257.6497726400048</v>
+        <v>-257.6497717371312</v>
       </c>
       <c r="O16">
-        <v>-446.5424707500024</v>
+        <v>-446.542469208769</v>
       </c>
       <c r="P16">
-        <v>-888.6706369999993</v>
+        <v>-888.6706340198107</v>
       </c>
       <c r="S16">
         <v>16</v>
@@ -2116,19 +2116,19 @@
         <v>16</v>
       </c>
       <c r="U16">
-        <v>-132.4113316920029</v>
+        <v>-132.4113311983274</v>
       </c>
       <c r="V16">
-        <v>-227.2712457300004</v>
+        <v>-227.2712450095678</v>
       </c>
       <c r="W16">
-        <v>-454.5424956599982</v>
+        <v>-454.5424942924183</v>
       </c>
       <c r="X16">
-        <v>-725.1922914399984</v>
+        <v>-725.1922892588063</v>
       </c>
       <c r="Y16">
-        <v>-1306.07757542</v>
+        <v>-1306.077571570686</v>
       </c>
       <c r="AB16">
         <v>16</v>
@@ -2137,19 +2137,19 @@
         <v>17</v>
       </c>
       <c r="AD16">
-        <v>-103.8599097960005</v>
+        <v>-103.8599095270392</v>
       </c>
       <c r="AE16">
-        <v>-109.1356143200001</v>
+        <v>-109.1356140632934</v>
       </c>
       <c r="AF16">
-        <v>-193.8926960599993</v>
+        <v>-193.8926956998276</v>
       </c>
       <c r="AG16">
-        <v>-303.0283152100001</v>
+        <v>-303.0283145909098</v>
       </c>
       <c r="AH16">
-        <v>-620.642322130001</v>
+        <v>-620.6423208534916</v>
       </c>
       <c r="AK16">
         <v>16</v>
@@ -2158,19 +2158,19 @@
         <v>11</v>
       </c>
       <c r="AM16">
-        <v>-1161.024940739997</v>
+        <v>-1161.024935413559</v>
       </c>
       <c r="AN16">
-        <v>-627.7495733599935</v>
+        <v>-627.7495704766625</v>
       </c>
       <c r="AO16">
-        <v>-955.2279402499844</v>
+        <v>-955.227935871706</v>
       </c>
       <c r="AP16">
-        <v>-1366.46337499001</v>
+        <v>-1366.463368750628</v>
       </c>
       <c r="AQ16">
-        <v>-3365.676325020009</v>
+        <v>-3365.676309614864</v>
       </c>
       <c r="AT16">
         <v>16</v>
@@ -2179,19 +2179,19 @@
         <v>12</v>
       </c>
       <c r="AV16">
-        <v>-667.5165362639964</v>
+        <v>-667.5165344477937</v>
       </c>
       <c r="AW16">
-        <v>-388.7138323900072</v>
+        <v>-388.713831041634</v>
       </c>
       <c r="AX16">
-        <v>-611.371183660005</v>
+        <v>-611.3711823412013</v>
       </c>
       <c r="AY16">
-        <v>-875.885416860001</v>
+        <v>-875.8854144480501</v>
       </c>
       <c r="AZ16">
-        <v>-2160.413130910005</v>
+        <v>-2160.413125316962</v>
       </c>
     </row>
     <row r="17" spans="1:52">
@@ -2202,19 +2202,19 @@
         <v>14</v>
       </c>
       <c r="C17">
-        <v>34.68313143000046</v>
+        <v>34.68313144754097</v>
       </c>
       <c r="D17">
-        <v>23.99999355999989</v>
+        <v>23.99999358029572</v>
       </c>
       <c r="E17">
-        <v>19.79214944000023</v>
+        <v>19.79214946880029</v>
       </c>
       <c r="F17">
-        <v>25.58430184000008</v>
+        <v>25.5843018583937</v>
       </c>
       <c r="G17">
-        <v>13.76599736999992</v>
+        <v>13.76599741397899</v>
       </c>
       <c r="J17">
         <v>11</v>
@@ -2223,19 +2223,19 @@
         <v>15</v>
       </c>
       <c r="L17">
-        <v>18.74039588399956</v>
+        <v>18.74039584034017</v>
       </c>
       <c r="M17">
-        <v>-29.01306949999889</v>
+        <v>-29.01306952814593</v>
       </c>
       <c r="N17">
-        <v>-70.84444555999926</v>
+        <v>-70.84444562620683</v>
       </c>
       <c r="O17">
-        <v>-122.2732038100003</v>
+        <v>-122.2732039088878</v>
       </c>
       <c r="P17">
-        <v>-262.1699415600005</v>
+        <v>-262.1699417378059</v>
       </c>
       <c r="S17">
         <v>11</v>
@@ -2244,19 +2244,19 @@
         <v>16</v>
       </c>
       <c r="U17">
-        <v>-30.35842495199904</v>
+        <v>-30.35842495302222</v>
       </c>
       <c r="V17">
-        <v>-66.03921696999987</v>
+        <v>-66.03921698459544</v>
       </c>
       <c r="W17">
-        <v>-141.0915091699999</v>
+        <v>-141.0915091929637</v>
       </c>
       <c r="X17">
-        <v>-228.3516445499999</v>
+        <v>-228.3516445909763</v>
       </c>
       <c r="Y17">
-        <v>-398.8719169300002</v>
+        <v>-398.8719170290506</v>
       </c>
       <c r="AB17">
         <v>11</v>
@@ -2265,19 +2265,19 @@
         <v>17</v>
       </c>
       <c r="AD17">
-        <v>-36.15608381400034</v>
+        <v>-36.15608379325568</v>
       </c>
       <c r="AE17">
-        <v>-37.44183888999987</v>
+        <v>-37.44183887599456</v>
       </c>
       <c r="AF17">
-        <v>-63.67583341</v>
+        <v>-63.6758333839316</v>
       </c>
       <c r="AG17">
-        <v>-101.9229025200002</v>
+        <v>-101.9229024735605</v>
       </c>
       <c r="AH17">
-        <v>-216.6641083299996</v>
+        <v>-216.6641082371002</v>
       </c>
       <c r="AK17">
         <v>11</v>
@@ -2286,19 +2286,19 @@
         <v>11</v>
       </c>
       <c r="AM17">
-        <v>-312.3051334499978</v>
+        <v>-312.3051336310054</v>
       </c>
       <c r="AN17">
-        <v>-170.7019794099979</v>
+        <v>-170.701979505593</v>
       </c>
       <c r="AO17">
-        <v>-256.7542779400028</v>
+        <v>-256.7542780817203</v>
       </c>
       <c r="AP17">
-        <v>-366.4170347999971</v>
+        <v>-366.4170350016575</v>
       </c>
       <c r="AQ17">
-        <v>-905.5360488699988</v>
+        <v>-905.5360493686604</v>
       </c>
       <c r="AT17">
         <v>11</v>
@@ -2307,19 +2307,19 @@
         <v>12</v>
       </c>
       <c r="AV17">
-        <v>-266.9937497399987</v>
+        <v>-266.9937498003674</v>
       </c>
       <c r="AW17">
-        <v>-209.3647210499985</v>
+        <v>-209.3647211010229</v>
       </c>
       <c r="AX17">
-        <v>-159.7412220800052</v>
+        <v>-159.7412221803952</v>
       </c>
       <c r="AY17">
-        <v>-236.6118253400036</v>
+        <v>-236.611825527576</v>
       </c>
       <c r="AZ17">
-        <v>-656.1988314199989</v>
+        <v>-656.1988318973836</v>
       </c>
     </row>
     <row r="18" spans="1:52">
@@ -2330,19 +2330,19 @@
         <v>14</v>
       </c>
       <c r="C18">
-        <v>11.51731935599992</v>
+        <v>11.51731933502185</v>
       </c>
       <c r="D18">
-        <v>5.000000239999963</v>
+        <v>5.000000231233912</v>
       </c>
       <c r="E18">
-        <v>3.40223570000012</v>
+        <v>3.402235668644608</v>
       </c>
       <c r="F18">
-        <v>4.603351259999954</v>
+        <v>4.603351227910707</v>
       </c>
       <c r="G18">
-        <v>-3.98882464999997</v>
+        <v>-3.988824717786542</v>
       </c>
       <c r="J18">
         <v>14</v>
@@ -2351,19 +2351,19 @@
         <v>15</v>
       </c>
       <c r="L18">
-        <v>10.55531175600026</v>
+        <v>10.55531174006319</v>
       </c>
       <c r="M18">
-        <v>-9.793293220000123</v>
+        <v>-9.793293252970216</v>
       </c>
       <c r="N18">
-        <v>-34.17876607000017</v>
+        <v>-34.17876609846599</v>
       </c>
       <c r="O18">
-        <v>-57.56423864999988</v>
+        <v>-57.56423869616492</v>
       </c>
       <c r="P18">
-        <v>-117.9273659500004</v>
+        <v>-117.9273660410154</v>
       </c>
       <c r="S18">
         <v>14</v>
@@ -2372,19 +2372,19 @@
         <v>16</v>
       </c>
       <c r="U18">
-        <v>-8.40000400200006</v>
+        <v>-8.400003981582813</v>
       </c>
       <c r="V18">
-        <v>-29.38547906000031</v>
+        <v>-29.38547903384006</v>
       </c>
       <c r="W18">
-        <v>-65.56425242000023</v>
+        <v>-65.56425238848942</v>
       </c>
       <c r="X18">
-        <v>-105.5419100200002</v>
+        <v>-105.5419099755732</v>
       </c>
       <c r="Y18">
-        <v>-184.2961071000004</v>
+        <v>-184.2961070334741</v>
       </c>
       <c r="AB18">
         <v>14</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="AD18">
-        <v>-19.54860454200025</v>
+        <v>-19.54860453424226</v>
       </c>
       <c r="AE18">
-        <v>-25.98323690000007</v>
+        <v>-25.98323691911787</v>
       </c>
       <c r="AF18">
-        <v>-44.77094530999989</v>
+        <v>-44.77094532367892</v>
       </c>
       <c r="AG18">
-        <v>-72.55306427000028</v>
+        <v>-72.55306432936391</v>
       </c>
       <c r="AH18">
-        <v>-150.3016635299998</v>
+        <v>-150.3016636011073</v>
       </c>
       <c r="AK18">
         <v>14</v>
@@ -2414,19 +2414,19 @@
         <v>11</v>
       </c>
       <c r="AM18">
-        <v>-169.2469016279993</v>
+        <v>-169.2469016716605</v>
       </c>
       <c r="AN18">
-        <v>-91.75976251000066</v>
+        <v>-91.75976254164924</v>
       </c>
       <c r="AO18">
-        <v>-139.1396441300003</v>
+        <v>-139.139644168592</v>
       </c>
       <c r="AP18">
-        <v>-199.3128186499998</v>
+        <v>-199.3128187185484</v>
       </c>
       <c r="AQ18">
-        <v>-489.586517669999</v>
+        <v>-489.5865178289969</v>
       </c>
       <c r="AT18">
         <v>14</v>
@@ -2435,19 +2435,19 @@
         <v>12</v>
       </c>
       <c r="AV18">
-        <v>-120.5229131879996</v>
+        <v>-120.5229131198548</v>
       </c>
       <c r="AW18">
-        <v>-104.3296043000009</v>
+        <v>-104.3296043292566</v>
       </c>
       <c r="AX18">
-        <v>-141.5139573699998</v>
+        <v>-141.5139574197083</v>
       </c>
       <c r="AY18">
-        <v>-206.0726132199989</v>
+        <v>-206.0726134101787</v>
       </c>
       <c r="AZ18">
-        <v>-485.6927061099996</v>
+        <v>-485.6927064301362</v>
       </c>
     </row>
     <row r="19" spans="1:52">
@@ -2458,19 +2458,19 @@
         <v>14</v>
       </c>
       <c r="C19">
-        <v>12.39428695799984</v>
+        <v>12.39428692330341</v>
       </c>
       <c r="D19">
-        <v>5.621537630000034</v>
+        <v>5.621537583014174</v>
       </c>
       <c r="E19">
-        <v>0.0180314400002998</v>
+        <v>0.0180313880077847</v>
       </c>
       <c r="F19">
-        <v>-4.888971459999993</v>
+        <v>-4.888971532725577</v>
       </c>
       <c r="G19">
-        <v>-18.86609670000007</v>
+        <v>-18.86609685407814</v>
       </c>
       <c r="J19">
         <v>13</v>
@@ -2479,19 +2479,19 @@
         <v>15</v>
       </c>
       <c r="L19">
-        <v>24.22906620000049</v>
+        <v>24.22906639438224</v>
       </c>
       <c r="M19">
-        <v>-14.67726760999949</v>
+        <v>-14.67726750581778</v>
       </c>
       <c r="N19">
-        <v>-44.68999875999953</v>
+        <v>-44.68999871350343</v>
       </c>
       <c r="O19">
-        <v>-75.64308007000091</v>
+        <v>-75.64308005334078</v>
       </c>
       <c r="P19">
-        <v>-173.1954238400003</v>
+        <v>-173.1954239114148</v>
       </c>
       <c r="S19">
         <v>13</v>
@@ -2500,19 +2500,19 @@
         <v>16</v>
       </c>
       <c r="U19">
-        <v>-14.21580783000081</v>
+        <v>-14.21580791206088</v>
       </c>
       <c r="V19">
-        <v>-49.70074777000082</v>
+        <v>-49.70074797701272</v>
       </c>
       <c r="W19">
-        <v>-112.6085026000001</v>
+        <v>-112.6085030245522</v>
       </c>
       <c r="X19">
-        <v>-182.2114070100015</v>
+        <v>-182.2114076657053</v>
       </c>
       <c r="Y19">
-        <v>-319.116001370001</v>
+        <v>-319.116002518037</v>
       </c>
       <c r="AB19">
         <v>13</v>
@@ -2521,19 +2521,19 @@
         <v>17</v>
       </c>
       <c r="AD19">
-        <v>-33.41099698200014</v>
+        <v>-33.41099707658941</v>
       </c>
       <c r="AE19">
-        <v>-37.18870651000043</v>
+        <v>-37.1887066302902</v>
       </c>
       <c r="AF19">
-        <v>-66.56914849999976</v>
+        <v>-66.5691487159902</v>
       </c>
       <c r="AG19">
-        <v>-108.9244358800006</v>
+        <v>-108.9244361789752</v>
       </c>
       <c r="AH19">
-        <v>-232.1892981700002</v>
+        <v>-232.1892987624196</v>
       </c>
       <c r="AK19">
         <v>13</v>
@@ -2542,19 +2542,19 @@
         <v>11</v>
       </c>
       <c r="AM19">
-        <v>-288.5017378140001</v>
+        <v>-288.5017388884244</v>
       </c>
       <c r="AN19">
-        <v>-154.7109691499973</v>
+        <v>-154.7109697400683</v>
       </c>
       <c r="AO19">
-        <v>-236.5503222799962</v>
+        <v>-236.5503231501789</v>
       </c>
       <c r="AP19">
-        <v>-338.4239161900005</v>
+        <v>-338.4239174316426</v>
       </c>
       <c r="AQ19">
-        <v>-834.9849658400017</v>
+        <v>-834.9849689021848</v>
       </c>
       <c r="AT19">
         <v>13</v>
@@ -2563,19 +2563,19 @@
         <v>12</v>
       </c>
       <c r="AV19">
-        <v>-225.5738830019964</v>
+        <v>-225.5738835302418</v>
       </c>
       <c r="AW19">
-        <v>-170.5192350899997</v>
+        <v>-170.5192354467581</v>
       </c>
       <c r="AX19">
-        <v>-159.0628058200018</v>
+        <v>-159.0628067955986</v>
       </c>
       <c r="AY19">
-        <v>-240.5679880899988</v>
+        <v>-240.5679891961408</v>
       </c>
       <c r="AZ19">
-        <v>-675.9736604499976</v>
+        <v>-675.9736630706648</v>
       </c>
     </row>
     <row r="20" spans="1:52">
@@ -2586,19 +2586,19 @@
         <v>14</v>
       </c>
       <c r="C20">
-        <v>84.85578731399892</v>
+        <v>84.85578712280585</v>
       </c>
       <c r="D20">
-        <v>53.00002334999772</v>
+        <v>53.0000232264365</v>
       </c>
       <c r="E20">
-        <v>65.00002777000009</v>
+        <v>65.0000276386736</v>
       </c>
       <c r="F20">
-        <v>82.28690910999921</v>
+        <v>82.28690893240218</v>
       </c>
       <c r="G20">
-        <v>67.4344100999997</v>
+        <v>67.43440992486649</v>
       </c>
       <c r="J20">
         <v>12</v>
@@ -2607,19 +2607,19 @@
         <v>15</v>
       </c>
       <c r="L20">
-        <v>51.42302670600293</v>
+        <v>51.42302656884021</v>
       </c>
       <c r="M20">
-        <v>-32.00000200000432</v>
+        <v>-32.00000200375507</v>
       </c>
       <c r="N20">
-        <v>-109.8525374700021</v>
+        <v>-109.8525373808625</v>
       </c>
       <c r="O20">
-        <v>-209.9919466200008</v>
+        <v>-209.9919463804617</v>
       </c>
       <c r="P20">
-        <v>-496.115153550003</v>
+        <v>-496.1151529222807</v>
       </c>
       <c r="S20">
         <v>12</v>
@@ -2628,19 +2628,19 @@
         <v>16</v>
       </c>
       <c r="U20">
-        <v>-71.65579211999466</v>
+        <v>-71.65579197555053</v>
       </c>
       <c r="V20">
-        <v>-135.9919438899979</v>
+        <v>-135.9919436214332</v>
       </c>
       <c r="W20">
-        <v>-273.1232558799984</v>
+        <v>-273.1232553416867</v>
       </c>
       <c r="X20">
-        <v>-436.9677092200018</v>
+        <v>-436.9677083331408</v>
       </c>
       <c r="Y20">
-        <v>-788.3697478099984</v>
+        <v>-788.3697462034343</v>
       </c>
       <c r="AB20">
         <v>12</v>
@@ -2649,19 +2649,19 @@
         <v>17</v>
       </c>
       <c r="AD20">
-        <v>-76.45090282199999</v>
+        <v>-76.45090262266604</v>
       </c>
       <c r="AE20">
-        <v>-75.27877353999884</v>
+        <v>-75.27877335841549</v>
       </c>
       <c r="AF20">
-        <v>-137.5575365800005</v>
+        <v>-137.5575362738582</v>
       </c>
       <c r="AG20">
-        <v>-217.5494259599982</v>
+        <v>-217.5494254857877</v>
       </c>
       <c r="AH20">
-        <v>-435.0988701799997</v>
+        <v>-435.0988691953353</v>
       </c>
       <c r="AK20">
         <v>12</v>
@@ -2670,19 +2670,19 @@
         <v>11</v>
       </c>
       <c r="AM20">
-        <v>-695.5681181159962</v>
+        <v>-695.5681161973771</v>
       </c>
       <c r="AN20">
-        <v>-376.951311949997</v>
+        <v>-376.9513109059917</v>
       </c>
       <c r="AO20">
-        <v>-574.6400955200079</v>
+        <v>-574.6400939663217</v>
       </c>
       <c r="AP20">
-        <v>-820.8945122699952</v>
+        <v>-820.8945100490091</v>
       </c>
       <c r="AQ20">
-        <v>-2027.740335979994</v>
+        <v>-2027.740330476452</v>
       </c>
       <c r="AT20">
         <v>12</v>
@@ -2691,19 +2691,19 @@
         <v>12</v>
       </c>
       <c r="AV20">
-        <v>-426.8169413159958</v>
+        <v>-426.8169400215375</v>
       </c>
       <c r="AW20">
-        <v>-168.9838717099992</v>
+        <v>-168.9838710193326</v>
       </c>
       <c r="AX20">
-        <v>-291.5414227199908</v>
+        <v>-291.5414219527811</v>
       </c>
       <c r="AY20">
-        <v>-417.8120896200016</v>
+        <v>-417.81208845113</v>
       </c>
       <c r="AZ20">
-        <v>-1269.591818219993</v>
+        <v>-1269.591815214331</v>
       </c>
     </row>
     <row r="21" spans="1:52">
@@ -2714,19 +2714,19 @@
         <v>14</v>
       </c>
       <c r="C21">
-        <v>271.799774592002</v>
+        <v>271.7997745162793</v>
       </c>
       <c r="D21">
-        <v>195.9998353399988</v>
+        <v>195.9998352886887</v>
       </c>
       <c r="E21">
-        <v>266.9997753900007</v>
+        <v>266.9997753176631</v>
       </c>
       <c r="F21">
-        <v>366.9996998999977</v>
+        <v>366.9996998102615</v>
       </c>
       <c r="G21">
-        <v>458.9996054399999</v>
+        <v>458.9996053165905</v>
       </c>
       <c r="J21">
         <v>28</v>
@@ -2735,19 +2735,19 @@
         <v>15</v>
       </c>
       <c r="L21">
-        <v>-3.000003275999916</v>
+        <v>-3.000003269706212</v>
       </c>
       <c r="M21">
-        <v>-85.99995203000435</v>
+        <v>-85.99995198640318</v>
       </c>
       <c r="N21">
-        <v>-237.9998528299984</v>
+        <v>-237.9998527324606</v>
       </c>
       <c r="O21">
-        <v>-424.9997308999991</v>
+        <v>-424.9997307341</v>
       </c>
       <c r="P21">
-        <v>-837.9994780999987</v>
+        <v>-837.9994777948777</v>
       </c>
       <c r="S21">
         <v>28</v>
@@ -2756,19 +2756,19 @@
         <v>16</v>
       </c>
       <c r="U21">
-        <v>-193.1998359180034</v>
+        <v>-193.199835866988</v>
       </c>
       <c r="V21">
-        <v>-254.9997910400016</v>
+        <v>-254.9997909729464</v>
       </c>
       <c r="W21">
-        <v>-468.9996264899983</v>
+        <v>-468.9996263637713</v>
       </c>
       <c r="X21">
-        <v>-750.9994013800006</v>
+        <v>-750.9994011859853</v>
       </c>
       <c r="Y21">
-        <v>-1370.998905139999</v>
+        <v>-1370.998904803515</v>
       </c>
       <c r="AB21">
         <v>28</v>
@@ -2777,19 +2777,19 @@
         <v>17</v>
       </c>
       <c r="AD21">
-        <v>-99.59991701400033</v>
+        <v>-99.59991699531474</v>
       </c>
       <c r="AE21">
-        <v>-87.99992436999946</v>
+        <v>-87.99992435570857</v>
       </c>
       <c r="AF21">
-        <v>-130.9998985299999</v>
+        <v>-130.9998984776812</v>
       </c>
       <c r="AG21">
-        <v>-193.9998523999993</v>
+        <v>-193.9998523280628</v>
       </c>
       <c r="AH21">
-        <v>-420.9996649200002</v>
+        <v>-420.9996647724192</v>
       </c>
       <c r="AK21">
         <v>28</v>
@@ -2798,19 +2798,19 @@
         <v>11</v>
       </c>
       <c r="AM21">
-        <v>-1075.199160006014</v>
+        <v>-1075.199159651696</v>
       </c>
       <c r="AN21">
-        <v>-581.9995497099953</v>
+        <v>-581.9995495246258</v>
       </c>
       <c r="AO21">
-        <v>-886.9993152700044</v>
+        <v>-886.9993149844959</v>
       </c>
       <c r="AP21">
-        <v>-1269.999015329995</v>
+        <v>-1269.99901492113</v>
       </c>
       <c r="AQ21">
-        <v>-3124.997582609991</v>
+        <v>-3124.997581605683</v>
       </c>
       <c r="AT21">
         <v>28</v>
@@ -2819,19 +2819,19 @@
         <v>12</v>
       </c>
       <c r="AV21">
-        <v>-914.9991958979954</v>
+        <v>-914.9991957765742</v>
       </c>
       <c r="AW21">
-        <v>-473.9995453400043</v>
+        <v>-473.9995453135271</v>
       </c>
       <c r="AX21">
-        <v>-518.9995323600087</v>
+        <v>-518.9995321363967</v>
       </c>
       <c r="AY21">
-        <v>-715.9994224900001</v>
+        <v>-715.9994223012181</v>
       </c>
       <c r="AZ21">
-        <v>-2132.998260420005</v>
+        <v>-2132.998259952328</v>
       </c>
     </row>
     <row r="22" spans="1:52">
@@ -2842,19 +2842,19 @@
         <v>14</v>
       </c>
       <c r="C22">
-        <v>138.4321106040006</v>
+        <v>138.4321106818234</v>
       </c>
       <c r="D22">
-        <v>73.57340268999906</v>
+        <v>73.57340273361842</v>
       </c>
       <c r="E22">
-        <v>85.57340853000005</v>
+        <v>85.57340857991858</v>
       </c>
       <c r="F22">
-        <v>112.8601119899995</v>
+        <v>112.8601120639405</v>
       </c>
       <c r="G22">
-        <v>116.5734132299995</v>
+        <v>116.5734133562191</v>
       </c>
       <c r="J22">
         <v>18</v>
@@ -2863,19 +2863,19 @@
         <v>15</v>
       </c>
       <c r="L22">
-        <v>34.03214094599934</v>
+        <v>34.03214086347543</v>
       </c>
       <c r="M22">
-        <v>-98.57336962999943</v>
+        <v>-98.573369691856</v>
       </c>
       <c r="N22">
-        <v>-255.0068482299993</v>
+        <v>-255.0068483271461</v>
       </c>
       <c r="O22">
-        <v>-425.4403246500005</v>
+        <v>-425.4403247945484</v>
       </c>
       <c r="P22">
-        <v>-818.8806801499995</v>
+        <v>-818.880680379636</v>
       </c>
       <c r="S22">
         <v>18</v>
@@ -2884,19 +2884,19 @@
         <v>16</v>
       </c>
       <c r="U22">
-        <v>-121.4181358080004</v>
+        <v>-121.4181358126425</v>
       </c>
       <c r="V22">
-        <v>-199.6502593800014</v>
+        <v>-199.6502593215719</v>
       </c>
       <c r="W22">
-        <v>-396.9438670400014</v>
+        <v>-396.9438669222454</v>
       </c>
       <c r="X22">
-        <v>-635.8808222099997</v>
+        <v>-635.880822033876</v>
       </c>
       <c r="Y22">
-        <v>-1160.971499370002</v>
+        <v>-1160.971499038382</v>
       </c>
       <c r="AB22">
         <v>18</v>
@@ -2905,19 +2905,19 @@
         <v>17</v>
       </c>
       <c r="AD22">
-        <v>-70.41813877199957</v>
+        <v>-70.41813875247453</v>
       </c>
       <c r="AE22">
-        <v>-65.14680620000036</v>
+        <v>-65.1468061581395</v>
       </c>
       <c r="AF22">
-        <v>-123.293601039999</v>
+        <v>-123.2936009922678</v>
       </c>
       <c r="AG22">
-        <v>-193.0837490300005</v>
+        <v>-193.0837489424111</v>
       </c>
       <c r="AH22">
-        <v>-401.8108579300001</v>
+        <v>-401.8108577212693</v>
       </c>
       <c r="AK22">
         <v>18</v>
@@ -2926,19 +2926,19 @@
         <v>11</v>
       </c>
       <c r="AM22">
-        <v>-487.0570563420079</v>
+        <v>-487.0570564879126</v>
       </c>
       <c r="AN22">
-        <v>-264.5872533600086</v>
+        <v>-264.5872534430855</v>
       </c>
       <c r="AO22">
-        <v>-400.8808823899999</v>
+        <v>-400.8808825095766</v>
       </c>
       <c r="AP22">
-        <v>-572.7479163499993</v>
+        <v>-572.747916529057</v>
       </c>
       <c r="AQ22">
-        <v>-1412.08308434</v>
+        <v>-1412.083084786864</v>
       </c>
       <c r="AT22">
         <v>18</v>
@@ -2947,19 +2947,19 @@
         <v>12</v>
       </c>
       <c r="AV22">
-        <v>-517.9508054159996</v>
+        <v>-517.9508053987738</v>
       </c>
       <c r="AW22">
-        <v>-284.5103672999976</v>
+        <v>-284.5103672777077</v>
       </c>
       <c r="AX22">
-        <v>-606.9507033000009</v>
+        <v>-606.9507033136542</v>
       </c>
       <c r="AY22">
-        <v>-859.6778034100025</v>
+        <v>-859.6778033161099</v>
       </c>
       <c r="AZ22">
-        <v>-1976.152774399997</v>
+        <v>-1976.152774011618</v>
       </c>
     </row>
     <row r="23" spans="1:52">
@@ -2970,19 +2970,19 @@
         <v>14</v>
       </c>
       <c r="C23">
-        <v>12.93449305800004</v>
+        <v>12.93449307774563</v>
       </c>
       <c r="D23">
-        <v>6.071585629999845</v>
+        <v>6.071585651484611</v>
       </c>
       <c r="E23">
-        <v>1.864433089999693</v>
+        <v>1.864433107559307</v>
       </c>
       <c r="F23">
-        <v>0.4859095599998682</v>
+        <v>0.4859095763969208</v>
       </c>
       <c r="G23">
-        <v>-15.30691674000013</v>
+        <v>-15.30691669734779</v>
       </c>
       <c r="J23">
         <v>19</v>
@@ -2991,19 +2991,19 @@
         <v>15</v>
       </c>
       <c r="L23">
-        <v>16.69717660799915</v>
+        <v>16.69717659312391</v>
       </c>
       <c r="M23">
-        <v>-13.07157672000085</v>
+        <v>-13.07157671295727</v>
       </c>
       <c r="N23">
-        <v>-41.35030713000015</v>
+        <v>-41.35030713788092</v>
       </c>
       <c r="O23">
-        <v>-72.45766648000063</v>
+        <v>-72.4576664781257</v>
       </c>
       <c r="P23">
-        <v>-154.3296482000001</v>
+        <v>-154.3296482211458</v>
       </c>
       <c r="S23">
         <v>19</v>
@@ -3012,19 +3012,19 @@
         <v>16</v>
       </c>
       <c r="U23">
-        <v>-10.38872863199958</v>
+        <v>-10.38872864294399</v>
       </c>
       <c r="V23">
-        <v>-38.72884092999993</v>
+        <v>-38.7288409172852</v>
       </c>
       <c r="W23">
-        <v>-86.45767466999996</v>
+        <v>-86.45767464665914</v>
       </c>
       <c r="X23">
-        <v>-137.8079846399987</v>
+        <v>-137.8079845903712</v>
       </c>
       <c r="Y23">
-        <v>-256.9229008300008</v>
+        <v>-256.9229007406097</v>
       </c>
       <c r="AB23">
         <v>19</v>
@@ -3033,19 +3033,19 @@
         <v>17</v>
       </c>
       <c r="AD23">
-        <v>-26.9401178940002</v>
+        <v>-26.94011788145553</v>
       </c>
       <c r="AE23">
-        <v>-30.86440883000023</v>
+        <v>-30.86440882833768</v>
       </c>
       <c r="AF23">
-        <v>-60.10734022000042</v>
+        <v>-60.10734019955044</v>
       </c>
       <c r="AG23">
-        <v>-94.97174520000044</v>
+        <v>-94.97174517996018</v>
       </c>
       <c r="AH23">
-        <v>-196.3578012999997</v>
+        <v>-196.3578012504217</v>
       </c>
       <c r="AK23">
         <v>19</v>
@@ -3054,19 +3054,19 @@
         <v>11</v>
       </c>
       <c r="AM23">
-        <v>-174.5752130819983</v>
+        <v>-174.575213268512</v>
       </c>
       <c r="AN23">
-        <v>-94.2505109699996</v>
+        <v>-94.25051107724356</v>
       </c>
       <c r="AO23">
-        <v>-143.7721863000024</v>
+        <v>-143.7721864629293</v>
       </c>
       <c r="AP23">
-        <v>-206.5368073599984</v>
+        <v>-206.5368075905444</v>
       </c>
       <c r="AQ23">
-        <v>-506.3241265299985</v>
+        <v>-506.3241270927265</v>
       </c>
       <c r="AT23">
         <v>19</v>
@@ -3075,19 +3075,19 @@
         <v>12</v>
       </c>
       <c r="AV23">
-        <v>-162.883666073998</v>
+        <v>-162.8836660170946</v>
       </c>
       <c r="AW23">
-        <v>-107.2863032199984</v>
+        <v>-107.2863032943369</v>
       </c>
       <c r="AX23">
-        <v>-158.6290019100015</v>
+        <v>-158.629001795367</v>
       </c>
       <c r="AY23">
-        <v>-209.1148739000018</v>
+        <v>-209.1148738148422</v>
       </c>
       <c r="AZ23">
-        <v>-521.5876111100006</v>
+        <v>-521.5876108398625</v>
       </c>
     </row>
     <row r="24" spans="1:52">
@@ -3098,19 +3098,19 @@
         <v>14</v>
       </c>
       <c r="C24">
-        <v>61.31695894799986</v>
+        <v>61.3169590106204</v>
       </c>
       <c r="D24">
-        <v>38.00004373999991</v>
+        <v>38.0000437769495</v>
       </c>
       <c r="E24">
-        <v>28.2078114599999</v>
+        <v>28.20781152421659</v>
       </c>
       <c r="F24">
-        <v>30.4155810100001</v>
+        <v>30.4155811085102</v>
       </c>
       <c r="G24">
-        <v>6.233656610000253</v>
+        <v>6.233656720487033</v>
       </c>
       <c r="J24">
         <v>20</v>
@@ -3119,19 +3119,19 @@
         <v>15</v>
       </c>
       <c r="L24">
-        <v>38.25978813599977</v>
+        <v>38.25978814222981</v>
       </c>
       <c r="M24">
-        <v>-52.98723515999882</v>
+        <v>-52.98723517168219</v>
       </c>
       <c r="N24">
-        <v>-131.1562086099984</v>
+        <v>-131.1562086709164</v>
       </c>
       <c r="O24">
-        <v>-226.727909180001</v>
+        <v>-226.7279092743556</v>
       </c>
       <c r="P24">
-        <v>-492.832310419999</v>
+        <v>-492.8323105372638</v>
       </c>
       <c r="S24">
         <v>20</v>
@@ -3140,19 +3140,19 @@
         <v>16</v>
       </c>
       <c r="U24">
-        <v>-53.64159713399931</v>
+        <v>-53.6415971964143</v>
       </c>
       <c r="V24">
-        <v>-125.9612455099996</v>
+        <v>-125.9612455688475</v>
       </c>
       <c r="W24">
-        <v>-274.909564030002</v>
+        <v>-274.9095640917094</v>
       </c>
       <c r="X24">
-        <v>-447.6501536899996</v>
+        <v>-447.6501537814638</v>
       </c>
       <c r="Y24">
-        <v>-789.1312150199992</v>
+        <v>-789.1312151292404</v>
       </c>
       <c r="AB24">
         <v>20</v>
@@ -3161,19 +3161,19 @@
         <v>17</v>
       </c>
       <c r="AD24">
-        <v>-69.44421071400029</v>
+        <v>-69.44421071158285</v>
       </c>
       <c r="AE24">
-        <v>-75.55854250000084</v>
+        <v>-75.55854249094045</v>
       </c>
       <c r="AF24">
-        <v>-125.3248906400004</v>
+        <v>-125.3248906389181</v>
       </c>
       <c r="AG24">
-        <v>-202.0781980099992</v>
+        <v>-202.0781980116535</v>
       </c>
       <c r="AH24">
-        <v>-430.3383215899994</v>
+        <v>-430.3383215880003</v>
       </c>
       <c r="AK24">
         <v>20</v>
@@ -3182,19 +3182,19 @@
         <v>11</v>
       </c>
       <c r="AM24">
-        <v>-605.6973760260007</v>
+        <v>-605.697376727956</v>
       </c>
       <c r="AN24">
-        <v>-328.299441220006</v>
+        <v>-328.2994416065703</v>
       </c>
       <c r="AO24">
-        <v>-500.2478324800104</v>
+        <v>-500.2478330686718</v>
       </c>
       <c r="AP24">
-        <v>-713.5859605700025</v>
+        <v>-713.5859614086803</v>
       </c>
       <c r="AQ24">
-        <v>-1755.471362010001</v>
+        <v>-1755.471364064775</v>
       </c>
       <c r="AT24">
         <v>20</v>
@@ -3203,19 +3203,19 @@
         <v>12</v>
       </c>
       <c r="AV24">
-        <v>-550.808834135998</v>
+        <v>-550.8088340768409</v>
       </c>
       <c r="AW24">
-        <v>-426.6372315999979</v>
+        <v>-426.6372315202752</v>
       </c>
       <c r="AX24">
-        <v>-348.2609766599999</v>
+        <v>-348.2609767524918</v>
       </c>
       <c r="AY24">
-        <v>-500.3903140399998</v>
+        <v>-500.3903140884649</v>
       </c>
       <c r="AZ24">
-        <v>-1384.808244470005</v>
+        <v>-1384.808244647873</v>
       </c>
     </row>
     <row r="25" spans="1:52">
@@ -3226,19 +3226,19 @@
         <v>14</v>
       </c>
       <c r="C25">
-        <v>260.3999963699971</v>
+        <v>260.3999966707488</v>
       </c>
       <c r="D25">
-        <v>161.0000010700005</v>
+        <v>161.0000012776854</v>
       </c>
       <c r="E25">
-        <v>153.0000192899988</v>
+        <v>153.0000195662706</v>
       </c>
       <c r="F25">
-        <v>190.0000372300001</v>
+        <v>190.0000376389908</v>
       </c>
       <c r="G25">
-        <v>167.0000691100013</v>
+        <v>167.0000696547104</v>
       </c>
       <c r="J25">
         <v>27</v>
@@ -3247,19 +3247,19 @@
         <v>15</v>
       </c>
       <c r="L25">
-        <v>80.3999625960023</v>
+        <v>80.3999625429642</v>
       </c>
       <c r="M25">
-        <v>-155.9999537399999</v>
+        <v>-155.999953748058</v>
       </c>
       <c r="N25">
-        <v>-396.9999100100104</v>
+        <v>-396.9999101029025</v>
       </c>
       <c r="O25">
-        <v>-669.9998413700087</v>
+        <v>-669.9998415121881</v>
       </c>
       <c r="P25">
-        <v>-1375.999656759999</v>
+        <v>-1375.999657044937</v>
       </c>
       <c r="S25">
         <v>27</v>
@@ -3268,19 +3268,19 @@
         <v>16</v>
       </c>
       <c r="U25">
-        <v>-221.3999974380022</v>
+        <v>-221.3999976947816</v>
       </c>
       <c r="V25">
-        <v>-423.999914210006</v>
+        <v>-423.9999143332461</v>
       </c>
       <c r="W25">
-        <v>-859.9997900600029</v>
+        <v>-859.9997901825045</v>
       </c>
       <c r="X25">
-        <v>-1366.99967139</v>
+        <v>-1366.999671575904</v>
       </c>
       <c r="Y25">
-        <v>-2370.999427099996</v>
+        <v>-2370.999427355779</v>
       </c>
       <c r="AB25">
         <v>27</v>
@@ -3289,19 +3289,19 @@
         <v>17</v>
       </c>
       <c r="AD25">
-        <v>-178.7999401500001</v>
+        <v>-178.7999401303205</v>
       </c>
       <c r="AE25">
-        <v>-186.9999089400008</v>
+        <v>-186.9999088769291</v>
       </c>
       <c r="AF25">
-        <v>-301.9998462700005</v>
+        <v>-301.9998461264258</v>
       </c>
       <c r="AG25">
-        <v>-467.9997375599996</v>
+        <v>-467.9997373139922</v>
       </c>
       <c r="AH25">
-        <v>-969.9994947900012</v>
+        <v>-969.9994942641242</v>
       </c>
       <c r="AK25">
         <v>27</v>
@@ -3310,19 +3310,19 @@
         <v>11</v>
       </c>
       <c r="AM25">
-        <v>-1802.999999232008</v>
+        <v>-1803.000002213273</v>
       </c>
       <c r="AN25">
-        <v>-976.9999976000108</v>
+        <v>-976.9999991960068</v>
       </c>
       <c r="AO25">
-        <v>-1490.999994009995</v>
+        <v>-1490.999996457016</v>
       </c>
       <c r="AP25">
-        <v>-2124.000005160008</v>
+        <v>-2124.000008652947</v>
       </c>
       <c r="AQ25">
-        <v>-5234.000001879991</v>
+        <v>-5234.000010453427</v>
       </c>
       <c r="AT25">
         <v>27</v>
@@ -3331,19 +3331,19 @@
         <v>12</v>
       </c>
       <c r="AV25">
-        <v>-1553.999584721998</v>
+        <v>-1553.999584661782</v>
       </c>
       <c r="AW25">
-        <v>-1179.999628059988</v>
+        <v>-1179.999627851299</v>
       </c>
       <c r="AX25">
-        <v>-1130.99962997</v>
+        <v>-1130.999629768499</v>
       </c>
       <c r="AY25">
-        <v>-1706.999408920004</v>
+        <v>-1706.999408603209</v>
       </c>
       <c r="AZ25">
-        <v>-4421.998546959992</v>
+        <v>-4421.998546095332</v>
       </c>
     </row>
     <row r="26" spans="1:52">
@@ -3354,19 +3354,19 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>100.5312637379993</v>
+        <v>100.5312638746245</v>
       </c>
       <c r="D26">
-        <v>62.37844170000062</v>
+        <v>62.3784417889965</v>
       </c>
       <c r="E26">
-        <v>70.42963226000029</v>
+        <v>70.42963238569928</v>
       </c>
       <c r="F26">
-        <v>89.78431791999901</v>
+        <v>89.78431810422398</v>
       </c>
       <c r="G26">
-        <v>96.5521607799992</v>
+        <v>96.55216103605289</v>
       </c>
       <c r="J26">
         <v>22</v>
@@ -3375,19 +3375,19 @@
         <v>15</v>
       </c>
       <c r="L26">
-        <v>8.69066703000135</v>
+        <v>8.690666943986798</v>
       </c>
       <c r="M26">
-        <v>-52.53201248000005</v>
+        <v>-52.53201253967745</v>
       </c>
       <c r="N26">
-        <v>-136.937843089996</v>
+        <v>-136.9378432341109</v>
       </c>
       <c r="O26">
-        <v>-227.0603259800009</v>
+        <v>-227.0603262334844</v>
       </c>
       <c r="P26">
-        <v>-453.8683159599987</v>
+        <v>-453.8683163899477</v>
       </c>
       <c r="S26">
         <v>22</v>
@@ -3396,19 +3396,19 @@
         <v>16</v>
       </c>
       <c r="U26">
-        <v>-77.91555576600058</v>
+        <v>-77.91555585391961</v>
       </c>
       <c r="V26">
-        <v>-136.3747480300008</v>
+        <v>-136.3747481048904</v>
       </c>
       <c r="W26">
-        <v>-264.6471206099986</v>
+        <v>-264.6471207174845</v>
       </c>
       <c r="X26">
-        <v>-425.3289758399988</v>
+        <v>-425.328975992521</v>
       </c>
       <c r="Y26">
-        <v>-749.0985791399989</v>
+        <v>-749.0985794263152</v>
       </c>
       <c r="AB26">
         <v>22</v>
@@ -3417,19 +3417,19 @@
         <v>17</v>
       </c>
       <c r="AD26">
-        <v>-50.42848900800027</v>
+        <v>-50.42848896817486</v>
       </c>
       <c r="AE26">
-        <v>-53.3344986900006</v>
+        <v>-53.33449865772173</v>
       </c>
       <c r="AF26">
-        <v>-83.92495826000049</v>
+        <v>-83.92495819287933</v>
       </c>
       <c r="AG26">
-        <v>-133.6451730200006</v>
+        <v>-133.6451728838533</v>
       </c>
       <c r="AH26">
-        <v>-284.0545398500003</v>
+        <v>-284.0545395751228</v>
       </c>
       <c r="AK26">
         <v>22</v>
@@ -3438,19 +3438,19 @@
         <v>11</v>
       </c>
       <c r="AM26">
-        <v>-527.8016849759988</v>
+        <v>-527.8016855858768</v>
       </c>
       <c r="AN26">
-        <v>-284.352952039997</v>
+        <v>-284.35295236811</v>
       </c>
       <c r="AO26">
-        <v>-433.8740384299999</v>
+        <v>-433.8740389382474</v>
       </c>
       <c r="AP26">
-        <v>-621.6748396299954</v>
+        <v>-621.6748403652055</v>
       </c>
       <c r="AQ26">
-        <v>-1531.828779320003</v>
+        <v>-1531.828781122571</v>
       </c>
       <c r="AT26">
         <v>22</v>
@@ -3459,19 +3459,19 @@
         <v>12</v>
       </c>
       <c r="AV26">
-        <v>-442.194309864004</v>
+        <v>-442.1943097902076</v>
       </c>
       <c r="AW26">
-        <v>-317.7071710800083</v>
+        <v>-317.707171010341</v>
       </c>
       <c r="AX26">
-        <v>-334.6580002299997</v>
+        <v>-334.6580002866358</v>
       </c>
       <c r="AY26">
-        <v>-451.2281405499962</v>
+        <v>-451.2281405717658</v>
       </c>
       <c r="AZ26">
-        <v>-1252.757945020006</v>
+        <v>-1252.757945075515</v>
       </c>
     </row>
     <row r="27" spans="1:52">
@@ -3482,19 +3482,19 @@
         <v>14</v>
       </c>
       <c r="C27">
-        <v>191.9999713079997</v>
+        <v>191.9999713363686</v>
       </c>
       <c r="D27">
-        <v>103.9999852599994</v>
+        <v>103.9999852979418</v>
       </c>
       <c r="E27">
-        <v>111.9999789700014</v>
+        <v>111.9999790685615</v>
       </c>
       <c r="F27">
-        <v>143.9999735800011</v>
+        <v>143.999973656737</v>
       </c>
       <c r="G27">
-        <v>106.9999826100011</v>
+        <v>106.9999827911979</v>
       </c>
       <c r="J27">
         <v>29</v>
@@ -3503,19 +3503,19 @@
         <v>15</v>
       </c>
       <c r="L27">
-        <v>101.3999095019972</v>
+        <v>101.3999094599312</v>
       </c>
       <c r="M27">
-        <v>-91.0000319100036</v>
+        <v>-91.00003187553013</v>
       </c>
       <c r="N27">
-        <v>-320.0000196299989</v>
+        <v>-320.00001951593</v>
       </c>
       <c r="O27">
-        <v>-549.9999998500025</v>
+        <v>-549.9999996623446</v>
       </c>
       <c r="P27">
-        <v>-1091.99996306</v>
+        <v>-1091.999962660157</v>
       </c>
       <c r="S27">
         <v>29</v>
@@ -3524,19 +3524,19 @@
         <v>16</v>
       </c>
       <c r="U27">
-        <v>-182.9999337540012</v>
+        <v>-182.9999338069647</v>
       </c>
       <c r="V27">
-        <v>-315.9998962099962</v>
+        <v>-315.9998961438723</v>
       </c>
       <c r="W27">
-        <v>-610.9997966299961</v>
+        <v>-610.9997964958566</v>
       </c>
       <c r="X27">
-        <v>-974.9996836099964</v>
+        <v>-974.9996833495788</v>
       </c>
       <c r="Y27">
-        <v>-1701.999474010001</v>
+        <v>-1701.999473535358</v>
       </c>
       <c r="AB27">
         <v>29</v>
@@ -3545,19 +3545,19 @@
         <v>17</v>
       </c>
       <c r="AD27">
-        <v>-151.7999279040005</v>
+        <v>-151.7999278253346</v>
       </c>
       <c r="AE27">
-        <v>-152.9999274599995</v>
+        <v>-152.9999274064976</v>
       </c>
       <c r="AF27">
-        <v>-249.9998732999993</v>
+        <v>-249.9998731796013</v>
       </c>
       <c r="AG27">
-        <v>-407.9997952300009</v>
+        <v>-407.9997949896215</v>
       </c>
       <c r="AH27">
-        <v>-809.9996136099999</v>
+        <v>-809.9996131096614</v>
       </c>
       <c r="AK27">
         <v>29</v>
@@ -3566,19 +3566,19 @@
         <v>11</v>
       </c>
       <c r="AM27">
-        <v>-1313.399487257993</v>
+        <v>-1313.399486066905</v>
       </c>
       <c r="AN27">
-        <v>-714.9997314299981</v>
+        <v>-714.9997307564045</v>
       </c>
       <c r="AO27">
-        <v>-1083.999601970019</v>
+        <v>-1083.999600965559</v>
       </c>
       <c r="AP27">
-        <v>-1548.999432259996</v>
+        <v>-1548.999430830605</v>
       </c>
       <c r="AQ27">
-        <v>-3820.998585540001</v>
+        <v>-3820.998582036147</v>
       </c>
       <c r="AT27">
         <v>29</v>
@@ -3587,19 +3587,19 @@
         <v>12</v>
       </c>
       <c r="AV27">
-        <v>-1113.599600208013</v>
+        <v>-1113.599599833782</v>
       </c>
       <c r="AW27">
-        <v>-640.9998528499927</v>
+        <v>-640.9998527675198</v>
       </c>
       <c r="AX27">
-        <v>-704.9998577399965</v>
+        <v>-704.9998579701496</v>
       </c>
       <c r="AY27">
-        <v>-1289.999788300003</v>
+        <v>-1289.999787632456</v>
       </c>
       <c r="AZ27">
-        <v>-3112.999156450016</v>
+        <v>-3112.999155279787</v>
       </c>
     </row>
     <row r="28" spans="1:52">
@@ -3610,19 +3610,19 @@
         <v>14</v>
       </c>
       <c r="C28">
-        <v>32.39894196599948</v>
+        <v>32.39894190032169</v>
       </c>
       <c r="D28">
-        <v>20.99932115000001</v>
+        <v>20.99932109755491</v>
       </c>
       <c r="E28">
-        <v>23.99927185999968</v>
+        <v>23.99927177574091</v>
       </c>
       <c r="F28">
-        <v>29.99913310999977</v>
+        <v>29.99913298507681</v>
       </c>
       <c r="G28">
-        <v>26.99936636999973</v>
+        <v>26.99936619217078</v>
       </c>
       <c r="J28">
         <v>21</v>
@@ -3631,19 +3631,19 @@
         <v>15</v>
       </c>
       <c r="L28">
-        <v>28.19882399399921</v>
+        <v>28.19882399666949</v>
       </c>
       <c r="M28">
-        <v>-3.000049570000556</v>
+        <v>-3.000049613810006</v>
       </c>
       <c r="N28">
-        <v>-30.99923934999969</v>
+        <v>-30.99923944511193</v>
       </c>
       <c r="O28">
-        <v>-66.99809105000077</v>
+        <v>-66.99809112477124</v>
       </c>
       <c r="P28">
-        <v>-168.9947219100004</v>
+        <v>-168.9947220458907</v>
       </c>
       <c r="S28">
         <v>21</v>
@@ -3652,19 +3652,19 @@
         <v>16</v>
       </c>
       <c r="U28">
-        <v>-26.99913427800038</v>
+        <v>-26.99913423129146</v>
       </c>
       <c r="V28">
-        <v>-51.9981978600008</v>
+        <v>-51.99819785609634</v>
       </c>
       <c r="W28">
-        <v>-110.996145009999</v>
+        <v>-110.9961450151131</v>
       </c>
       <c r="X28">
-        <v>-179.9937268100003</v>
+        <v>-179.993726817338</v>
       </c>
       <c r="Y28">
-        <v>-319.9890200600003</v>
+        <v>-319.9890200622167</v>
       </c>
       <c r="AB28">
         <v>21</v>
@@ -3673,19 +3673,19 @@
         <v>17</v>
       </c>
       <c r="AD28">
-        <v>-38.39848786799939</v>
+        <v>-38.39848785477488</v>
       </c>
       <c r="AE28">
-        <v>-37.99846977000107</v>
+        <v>-37.99846975679248</v>
       </c>
       <c r="AF28">
-        <v>-69.99718453999958</v>
+        <v>-69.99718450758428</v>
       </c>
       <c r="AG28">
-        <v>-105.9958310800002</v>
+        <v>-105.995831075802</v>
       </c>
       <c r="AH28">
-        <v>-218.9914107599998</v>
+        <v>-218.9914107436525</v>
       </c>
       <c r="AK28">
         <v>21</v>
@@ -3694,19 +3694,19 @@
         <v>11</v>
       </c>
       <c r="AM28">
-        <v>-323.3900972040028</v>
+        <v>-323.3900968709786</v>
       </c>
       <c r="AN28">
-        <v>-174.9946105500021</v>
+        <v>-174.9946103654584</v>
       </c>
       <c r="AO28">
-        <v>-264.9918732200022</v>
+        <v>-264.9918729606034</v>
       </c>
       <c r="AP28">
-        <v>-378.9884334999988</v>
+        <v>-378.9884331188223</v>
       </c>
       <c r="AQ28">
-        <v>-934.9715166599964</v>
+        <v>-934.9715157188076</v>
       </c>
       <c r="AT28">
         <v>21</v>
@@ -3715,19 +3715,19 @@
         <v>12</v>
       </c>
       <c r="AV28">
-        <v>-210.5921900760023</v>
+        <v>-210.592190115327</v>
       </c>
       <c r="AW28">
-        <v>-92.9964713499994</v>
+        <v>-92.99647140169692</v>
       </c>
       <c r="AX28">
-        <v>-155.9942241499994</v>
+        <v>-155.9942240514047</v>
       </c>
       <c r="AY28">
-        <v>-189.993380670001</v>
+        <v>-189.9933804260836</v>
       </c>
       <c r="AZ28">
-        <v>-576.9793594799994</v>
+        <v>-576.979359330584</v>
       </c>
     </row>
     <row r="29" spans="1:52">
@@ -3738,19 +3738,19 @@
         <v>14</v>
       </c>
       <c r="C29">
-        <v>64.20118310399903</v>
+        <v>64.20118318797677</v>
       </c>
       <c r="D29">
-        <v>26.00063955999985</v>
+        <v>26.00063961543856</v>
       </c>
       <c r="E29">
-        <v>19.00076114000012</v>
+        <v>19.00076121164784</v>
       </c>
       <c r="F29">
-        <v>16.00069038999845</v>
+        <v>16.00069050908769</v>
       </c>
       <c r="G29">
-        <v>-40.99983922000138</v>
+        <v>-40.9998391181357</v>
       </c>
       <c r="J29">
         <v>26</v>
@@ -3759,19 +3759,19 @@
         <v>15</v>
       </c>
       <c r="L29">
-        <v>102.6016078859957</v>
+        <v>102.6016078932589</v>
       </c>
       <c r="M29">
-        <v>-34.9999315999994</v>
+        <v>-34.99993160908707</v>
       </c>
       <c r="N29">
-        <v>-177.0012372999954</v>
+        <v>-177.0012373661029</v>
       </c>
       <c r="O29">
-        <v>-306.0023022799996</v>
+        <v>-306.0023024215188</v>
       </c>
       <c r="P29">
-        <v>-645.0065258499963</v>
+        <v>-645.0065261313848</v>
       </c>
       <c r="S29">
         <v>26</v>
@@ -3780,19 +3780,19 @@
         <v>16</v>
       </c>
       <c r="U29">
-        <v>-80.40103490400361</v>
+        <v>-80.4010349786513</v>
       </c>
       <c r="V29">
-        <v>-182.0025242100055</v>
+        <v>-182.0025243241107</v>
       </c>
       <c r="W29">
-        <v>-379.00536397</v>
+        <v>-379.0053641925133</v>
       </c>
       <c r="X29">
-        <v>-606.0087541499979</v>
+        <v>-606.0087545110564</v>
       </c>
       <c r="Y29">
-        <v>-1085.015304300001</v>
+        <v>-1085.01530496646</v>
       </c>
       <c r="AB29">
         <v>26</v>
@@ -3801,19 +3801,19 @@
         <v>17</v>
       </c>
       <c r="AD29">
-        <v>-105.6019708559998</v>
+        <v>-105.601970878648</v>
       </c>
       <c r="AE29">
-        <v>-98.0021514600021</v>
+        <v>-98.00215147396284</v>
       </c>
       <c r="AF29">
-        <v>-160.0037846699997</v>
+        <v>-160.0037847070143</v>
       </c>
       <c r="AG29">
-        <v>-277.0061943799983</v>
+        <v>-277.0061944290328</v>
       </c>
       <c r="AH29">
-        <v>-580.0120901000009</v>
+        <v>-580.0120901768669</v>
       </c>
       <c r="AK29">
         <v>26</v>
@@ -3822,19 +3822,19 @@
         <v>11</v>
       </c>
       <c r="AM29">
-        <v>-700.2112735440169</v>
+        <v>-700.2112736520648</v>
       </c>
       <c r="AN29">
-        <v>-381.0061257699781</v>
+        <v>-381.0061258399219</v>
       </c>
       <c r="AO29">
-        <v>-583.0092810500137</v>
+        <v>-583.0092811457871</v>
       </c>
       <c r="AP29">
-        <v>-832.013132939981</v>
+        <v>-832.0131330836521</v>
       </c>
       <c r="AQ29">
-        <v>-2049.032273079996</v>
+        <v>-2049.03227342305</v>
       </c>
       <c r="AT29">
         <v>26</v>
@@ -3843,19 +3843,19 @@
         <v>12</v>
       </c>
       <c r="AV29">
-        <v>-678.0105346079872</v>
+        <v>-678.0105347294884</v>
       </c>
       <c r="AW29">
-        <v>-301.0053621700208</v>
+        <v>-301.0053622603373</v>
       </c>
       <c r="AX29">
-        <v>-221.0080935600199</v>
+        <v>-221.0080939408581</v>
       </c>
       <c r="AY29">
-        <v>-520.0145319599906</v>
+        <v>-520.0145330601226</v>
       </c>
       <c r="AZ29">
-        <v>-1567.033853319997</v>
+        <v>-1567.033854728041</v>
       </c>
     </row>
     <row r="30" spans="1:52">
@@ -3866,19 +3866,19 @@
         <v>14</v>
       </c>
       <c r="C30">
-        <v>275.4005433480052</v>
+        <v>275.4005433070124</v>
       </c>
       <c r="D30">
-        <v>133.0004853900027</v>
+        <v>133.0004853620139</v>
       </c>
       <c r="E30">
-        <v>153.0006355499991</v>
+        <v>153.000635557275</v>
       </c>
       <c r="F30">
-        <v>174.0010378100014</v>
+        <v>174.0010378052029</v>
       </c>
       <c r="G30">
-        <v>119.0013928899953</v>
+        <v>119.0013929126526</v>
       </c>
       <c r="J30">
         <v>24</v>
@@ -3887,19 +3887,19 @@
         <v>15</v>
       </c>
       <c r="L30">
-        <v>101.3993894339947</v>
+        <v>101.3993893778788</v>
       </c>
       <c r="M30">
-        <v>-166.0004650699993</v>
+        <v>-166.0004650096525</v>
       </c>
       <c r="N30">
-        <v>-499.000427560004</v>
+        <v>-499.0004273590967</v>
       </c>
       <c r="O30">
-        <v>-813.0011023199986</v>
+        <v>-813.001101992053</v>
       </c>
       <c r="P30">
-        <v>-1563.001445310005</v>
+        <v>-1563.00144469419</v>
       </c>
       <c r="S30">
         <v>24</v>
@@ -3908,19 +3908,19 @@
         <v>16</v>
       </c>
       <c r="U30">
-        <v>-246.6002547960016</v>
+        <v>-246.6002547294884</v>
       </c>
       <c r="V30">
-        <v>-405.9997018299982</v>
+        <v>-405.9997016797679</v>
       </c>
       <c r="W30">
-        <v>-803.9993088899973</v>
+        <v>-803.9993086074974</v>
       </c>
       <c r="X30">
-        <v>-1268.998763579999</v>
+        <v>-1268.998763115742</v>
       </c>
       <c r="Y30">
-        <v>-2232.997848080005</v>
+        <v>-2232.997847240109</v>
       </c>
       <c r="AB30">
         <v>24</v>
@@ -3929,19 +3929,19 @@
         <v>17</v>
       </c>
       <c r="AD30">
-        <v>-166.7996781000011</v>
+        <v>-166.7996780452486</v>
       </c>
       <c r="AE30">
-        <v>-150.9994996199985</v>
+        <v>-150.9994995637344</v>
       </c>
       <c r="AF30">
-        <v>-251.9993426299998</v>
+        <v>-251.9993425467492</v>
       </c>
       <c r="AG30">
-        <v>-410.9983845000006</v>
+        <v>-410.9983843449354</v>
       </c>
       <c r="AH30">
-        <v>-825.9971958000024</v>
+        <v>-825.9971954658376</v>
       </c>
       <c r="AK30">
         <v>24</v>
@@ -3950,19 +3950,19 @@
         <v>11</v>
       </c>
       <c r="AM30">
-        <v>-1616.999316419984</v>
+        <v>-1616.999315776076</v>
       </c>
       <c r="AN30">
-        <v>-883.9996443800046</v>
+        <v>-883.9996440278192</v>
       </c>
       <c r="AO30">
-        <v>-1344.999392679994</v>
+        <v>-1344.999392144338</v>
       </c>
       <c r="AP30">
-        <v>-1918.999243400001</v>
+        <v>-1918.999242636826</v>
       </c>
       <c r="AQ30">
-        <v>-4729.998189300037</v>
+        <v>-4729.998187422694</v>
       </c>
       <c r="AT30">
         <v>24</v>
@@ -3971,19 +3971,19 @@
         <v>12</v>
       </c>
       <c r="AV30">
-        <v>-1303.798793381968</v>
+        <v>-1303.798792991249</v>
       </c>
       <c r="AW30">
-        <v>-755.9990224400099</v>
+        <v>-755.9990221844928</v>
       </c>
       <c r="AX30">
-        <v>-1205.000537040018</v>
+        <v>-1205.00053701282</v>
       </c>
       <c r="AY30">
-        <v>-1870.995324700008</v>
+        <v>-1870.995324178424</v>
       </c>
       <c r="AZ30">
-        <v>-4175.992516489976</v>
+        <v>-4175.992514693702</v>
       </c>
     </row>
     <row r="31" spans="1:52">
@@ -3994,19 +3994,19 @@
         <v>14</v>
       </c>
       <c r="C31">
-        <v>499.1992746540054</v>
+        <v>499.199274632203</v>
       </c>
       <c r="D31">
-        <v>296.9995354299972</v>
+        <v>296.9995354085877</v>
       </c>
       <c r="E31">
-        <v>408.9993132300042</v>
+        <v>408.9993131383708</v>
       </c>
       <c r="F31">
-        <v>492.9991097900056</v>
+        <v>492.9991096718622</v>
       </c>
       <c r="G31">
-        <v>424.999081549995</v>
+        <v>424.999081416503</v>
       </c>
       <c r="J31">
         <v>23</v>
@@ -4015,19 +4015,19 @@
         <v>15</v>
       </c>
       <c r="L31">
-        <v>4.800125286004914</v>
+        <v>4.800125276247854</v>
       </c>
       <c r="M31">
-        <v>-278.9995293800021</v>
+        <v>-278.9995294647597</v>
       </c>
       <c r="N31">
-        <v>-676.998978329997</v>
+        <v>-676.9989785221842</v>
       </c>
       <c r="O31">
-        <v>-1103.998319829989</v>
+        <v>-1103.998320093575</v>
       </c>
       <c r="P31">
-        <v>-2024.996933789989</v>
+        <v>-2024.996934327072</v>
       </c>
       <c r="S31">
         <v>23</v>
@@ -4036,19 +4036,19 @@
         <v>16</v>
       </c>
       <c r="U31">
-        <v>-355.7995118519975</v>
+        <v>-355.7995118344006</v>
       </c>
       <c r="V31">
-        <v>-484.999450820007</v>
+        <v>-484.9994508212476</v>
       </c>
       <c r="W31">
-        <v>-944.9989146700028</v>
+        <v>-944.9989146557964</v>
       </c>
       <c r="X31">
-        <v>-1450.998341999999</v>
+        <v>-1450.998342017188</v>
       </c>
       <c r="Y31">
-        <v>-2519.997091419998</v>
+        <v>-2519.997091501868</v>
       </c>
       <c r="AB31">
         <v>23</v>
@@ -4057,19 +4057,19 @@
         <v>17</v>
       </c>
       <c r="AD31">
-        <v>-197.9998075559997</v>
+        <v>-197.9998075388703</v>
       </c>
       <c r="AE31">
-        <v>-176.9998323699992</v>
+        <v>-176.9998323603022</v>
       </c>
       <c r="AF31">
-        <v>-324.9996198700019</v>
+        <v>-324.9996198319177</v>
       </c>
       <c r="AG31">
-        <v>-482.9994530000022</v>
+        <v>-482.9994530115782</v>
       </c>
       <c r="AH31">
-        <v>-936.998999179994</v>
+        <v>-936.9989991966432</v>
       </c>
       <c r="AK31">
         <v>23</v>
@@ -4078,19 +4078,19 @@
         <v>11</v>
       </c>
       <c r="AM31">
-        <v>-1694.999068074001</v>
+        <v>-1694.999067645942</v>
       </c>
       <c r="AN31">
-        <v>-927.9994858300053</v>
+        <v>-927.9994855812548</v>
       </c>
       <c r="AO31">
-        <v>-1410.99924450001</v>
+        <v>-1410.999244134509</v>
       </c>
       <c r="AP31">
-        <v>-2016.998902969994</v>
+        <v>-2016.998902429841</v>
       </c>
       <c r="AQ31">
-        <v>-4973.997294769972</v>
+        <v>-4973.997293457651</v>
       </c>
       <c r="AT31">
         <v>23</v>
@@ -4099,19 +4099,19 @@
         <v>12</v>
       </c>
       <c r="AV31">
-        <v>-1788.597910680008</v>
+        <v>-1788.597910637647</v>
       </c>
       <c r="AW31">
-        <v>-1031.998888979957</v>
+        <v>-1031.998888897302</v>
       </c>
       <c r="AX31">
-        <v>-2112.9968811</v>
+        <v>-2112.996880544713</v>
       </c>
       <c r="AY31">
-        <v>-2503.996076230003</v>
+        <v>-2503.99607610004</v>
       </c>
       <c r="AZ31">
-        <v>-5256.992876110016</v>
+        <v>-5256.992876344273</v>
       </c>
     </row>
     <row r="32" spans="1:52">
@@ -4122,19 +4122,19 @@
         <v>14</v>
       </c>
       <c r="C32">
-        <v>83.40002872199921</v>
+        <v>83.4000284101744</v>
       </c>
       <c r="D32">
-        <v>42.00001697000062</v>
+        <v>42.00001681619187</v>
       </c>
       <c r="E32">
-        <v>49.00002331999985</v>
+        <v>49.00002320986687</v>
       </c>
       <c r="F32">
-        <v>57.0000295599998</v>
+        <v>57.00002941822413</v>
       </c>
       <c r="G32">
-        <v>40.0000356999999</v>
+        <v>40.0000357005797</v>
       </c>
       <c r="J32">
         <v>25</v>
@@ -4143,19 +4143,19 @@
         <v>15</v>
       </c>
       <c r="L32">
-        <v>36.00001578600131</v>
+        <v>36.00001549795888</v>
       </c>
       <c r="M32">
-        <v>-57.99999001999822</v>
+        <v>-57.99998986288119</v>
       </c>
       <c r="N32">
-        <v>-168.9999871399996</v>
+        <v>-168.9999865192767</v>
       </c>
       <c r="O32">
-        <v>-279.9999808100019</v>
+        <v>-279.9999797486689</v>
       </c>
       <c r="P32">
-        <v>-546.99998065</v>
+        <v>-546.9999783594722</v>
       </c>
       <c r="S32">
         <v>25</v>
@@ -4164,19 +4164,19 @@
         <v>16</v>
       </c>
       <c r="U32">
-        <v>-78.60003517799942</v>
+        <v>-78.60003483072433</v>
       </c>
       <c r="V32">
-        <v>-136.0000335500008</v>
+        <v>-136.0000328833175</v>
       </c>
       <c r="W32">
-        <v>-264.000064580001</v>
+        <v>-264.0000632653137</v>
       </c>
       <c r="X32">
-        <v>-418.0001017900004</v>
+        <v>-418.0000996797917</v>
       </c>
       <c r="Y32">
-        <v>-741.0001776299987</v>
+        <v>-741.0001738393239</v>
       </c>
       <c r="AB32">
         <v>25</v>
@@ -4185,19 +4185,19 @@
         <v>17</v>
       </c>
       <c r="AD32">
-        <v>-55.20000944399999</v>
+        <v>-55.20000912664227</v>
       </c>
       <c r="AE32">
-        <v>-50.00000508999983</v>
+        <v>-50.00000479992286</v>
       </c>
       <c r="AF32">
-        <v>-89.00000566000017</v>
+        <v>-89.0000051668012</v>
       </c>
       <c r="AG32">
-        <v>-140.00001045</v>
+        <v>-140.0000096116573</v>
       </c>
       <c r="AH32">
-        <v>-279.0000398799998</v>
+        <v>-279.0000382114245</v>
       </c>
       <c r="AK32">
         <v>25</v>
@@ -4206,19 +4206,19 @@
         <v>11</v>
       </c>
       <c r="AM32">
-        <v>-422.4000229919948</v>
+        <v>-422.4000203866235</v>
       </c>
       <c r="AN32">
-        <v>-232.0000131000015</v>
+        <v>-232.0000116697265</v>
       </c>
       <c r="AO32">
-        <v>-352.0000213800013</v>
+        <v>-352.0000191912404</v>
       </c>
       <c r="AP32">
-        <v>-501.0000316500009</v>
+        <v>-501.000028539489</v>
       </c>
       <c r="AQ32">
-        <v>-1235.000085930002</v>
+        <v>-1235.000078230878</v>
       </c>
       <c r="AT32">
         <v>25</v>
@@ -4227,19 +4227,19 @@
         <v>12</v>
       </c>
       <c r="AV32">
-        <v>-377.4001806060005</v>
+        <v>-377.4001785280016</v>
       </c>
       <c r="AW32">
-        <v>-224.0000979200013</v>
+        <v>-224.0000969192916</v>
       </c>
       <c r="AX32">
-        <v>-358.0001668300029</v>
+        <v>-358.0001657216853</v>
       </c>
       <c r="AY32">
-        <v>-546.0002063800021</v>
+        <v>-546.0002040582913</v>
       </c>
       <c r="AZ32">
-        <v>-1207.000519519999</v>
+        <v>-1207.000513568899</v>
       </c>
     </row>
     <row r="33" spans="1:52">
